--- a/Research/Workflow Analysis/Workflow_Analysis.xlsx
+++ b/Research/Workflow Analysis/Workflow_Analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marci/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marci/Desktop/Notes/Research Space/Voice for Accessible Design/Creative-Visual-Design-Accessibility-Tools/Research/Workflow Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93539FA-D022-F74D-96DF-B0F264B448E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359B02B0-5809-4946-9E9F-CD8F015655F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-12280" yWindow="-19600" windowWidth="25720" windowHeight="17460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TEMPLATE" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="172">
   <si>
     <t>Title</t>
   </si>
@@ -385,9 +385,6 @@
     <t>zoom out viewport so all elements are in frame</t>
   </si>
   <si>
-    <t>[zoom] to show full context</t>
-  </si>
-  <si>
     <t>zoom in viewport to focus on image</t>
   </si>
   <si>
@@ -444,12 +441,126 @@
   <si>
     <t>[scroll] [gui panel]</t>
   </si>
+  <si>
+    <t>Let's Design Music Streaming App in Figma</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GfVA26-Z-SE</t>
+  </si>
+  <si>
+    <t>[hover] over [design object] in [layers panel]</t>
+  </si>
+  <si>
+    <t>[collapse] [group] on [layers panel]</t>
+  </si>
+  <si>
+    <t>[drag] to [multiselect] [design objects] on [canvas] using [cursor]</t>
+  </si>
+  <si>
+    <t>[ungroup] [selected] using [cursor]</t>
+  </si>
+  <si>
+    <t>align center for [selected]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">change autolayout width from hug to fixed width </t>
+  </si>
+  <si>
+    <t>select [layer name]</t>
+  </si>
+  <si>
+    <t>zoom out</t>
+  </si>
+  <si>
+    <t>drag</t>
+  </si>
+  <si>
+    <t>drag [selected] to [new position] - uses alignment grids</t>
+  </si>
+  <si>
+    <t>[create] [frame] from [selected]</t>
+  </si>
+  <si>
+    <t>[update] [design object name]</t>
+  </si>
+  <si>
+    <t>rename layer</t>
+  </si>
+  <si>
+    <t>[hover] over [design objects] in [layers panel]</t>
+  </si>
+  <si>
+    <t>hover over all design objects in layers panel</t>
+  </si>
+  <si>
+    <t>change figma page</t>
+  </si>
+  <si>
+    <t>[zoom] to fit context in viewport</t>
+  </si>
+  <si>
+    <t>[zoom] to focus [selected]</t>
+  </si>
+  <si>
+    <t>[drag] [selected] to [new position] using [cursor]</t>
+  </si>
+  <si>
+    <t>move selected to new position outside of the current frame</t>
+  </si>
+  <si>
+    <t>[pan]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[drag] [design object] to [resize] </t>
+  </si>
+  <si>
+    <t>layers panel</t>
+  </si>
+  <si>
+    <t>[hover] over [design objects] on [canvas]</t>
+  </si>
+  <si>
+    <t>align center</t>
+  </si>
+  <si>
+    <t>update autolayout property</t>
+  </si>
+  <si>
+    <t>update autolayout height from hug to fixed height</t>
+  </si>
+  <si>
+    <t>[select] [design object] on [layers panel] using [cursor]</t>
+  </si>
+  <si>
+    <t>add autolayout to selected</t>
+  </si>
+  <si>
+    <t>pan to centre of selected</t>
+  </si>
+  <si>
+    <t>align centre for selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">update autolayout height from hug to fixed height </t>
+  </si>
+  <si>
+    <t>update width to value</t>
+  </si>
+  <si>
+    <t>update height to value</t>
+  </si>
+  <si>
+    <t>rename</t>
+  </si>
+  <si>
+    <t>grouping</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,8 +600,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,6 +618,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -513,10 +637,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -532,8 +657,12 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5927,11 +6056,11 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <f t="shared" ref="Q194:Q225" si="38">P194-O194</f>
+        <f t="shared" ref="Q194:Q200" si="38">P194-O194</f>
         <v>0</v>
       </c>
       <c r="R194" t="str">
-        <f t="shared" ref="R194:R225" si="39">IF(Q194=0,"&lt;1 second","&lt;"&amp;(ROUND(Q194,2)+1)&amp;" seconds")</f>
+        <f t="shared" ref="R194:R200" si="39">IF(Q194=0,"&lt;1 second","&lt;"&amp;(ROUND(Q194,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S194">
@@ -8005,11 +8134,11 @@
         <v>40</v>
       </c>
       <c r="Q34">
-        <f t="shared" ref="Q34:Q65" si="8">P34-O34</f>
+        <f t="shared" ref="Q34:Q52" si="8">P34-O34</f>
         <v>0</v>
       </c>
       <c r="R34" t="str">
-        <f t="shared" ref="R34:R65" si="9">IF(Q34=0,"&lt;1 second","&lt;"&amp;(ROUND(Q34,2)+1)&amp;" seconds")</f>
+        <f t="shared" ref="R34:R52" si="9">IF(Q34=0,"&lt;1 second","&lt;"&amp;(ROUND(Q34,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S34" s="4">
@@ -9473,6 +9602,9 @@
       <c r="K3" t="s">
         <v>32</v>
       </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
       <c r="O3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -9517,6 +9649,9 @@
       <c r="K4" t="s">
         <v>32</v>
       </c>
+      <c r="M4" t="s">
+        <v>33</v>
+      </c>
       <c r="O4">
         <f t="shared" si="0"/>
         <v>4.0000000000000018</v>
@@ -9561,6 +9696,9 @@
       <c r="K5" t="s">
         <v>32</v>
       </c>
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
       <c r="O5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9605,6 +9743,9 @@
       <c r="K6" t="s">
         <v>32</v>
       </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
       <c r="O6">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9649,6 +9790,9 @@
       <c r="K7" t="s">
         <v>32</v>
       </c>
+      <c r="M7" t="s">
+        <v>40</v>
+      </c>
       <c r="O7">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -9693,6 +9837,9 @@
       <c r="K8" t="s">
         <v>32</v>
       </c>
+      <c r="M8" t="s">
+        <v>40</v>
+      </c>
       <c r="O8">
         <f t="shared" si="0"/>
         <v>18.000000000000004</v>
@@ -9737,6 +9884,9 @@
       <c r="K9" t="s">
         <v>32</v>
       </c>
+      <c r="M9" t="s">
+        <v>40</v>
+      </c>
       <c r="O9">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -9781,6 +9931,9 @@
       <c r="K10" t="s">
         <v>32</v>
       </c>
+      <c r="M10" t="s">
+        <v>40</v>
+      </c>
       <c r="O10">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -9825,6 +9978,9 @@
       <c r="K11" t="s">
         <v>32</v>
       </c>
+      <c r="M11" t="s">
+        <v>40</v>
+      </c>
       <c r="O11">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -9870,6 +10026,9 @@
       <c r="K12" t="s">
         <v>32</v>
       </c>
+      <c r="M12" t="s">
+        <v>40</v>
+      </c>
       <c r="O12">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -9905,8 +10064,8 @@
       <c r="F13" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>115</v>
+      <c r="G13" s="14" t="s">
+        <v>152</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
@@ -9948,7 +10107,7 @@
         <v>0.51</v>
       </c>
       <c r="F14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>77</v>
@@ -9958,6 +10117,9 @@
       </c>
       <c r="K14" t="s">
         <v>27</v>
+      </c>
+      <c r="M14" t="s">
+        <v>40</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
@@ -9992,16 +10154,19 @@
         <v>0.54</v>
       </c>
       <c r="F15" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I15" t="s">
         <v>26</v>
       </c>
       <c r="K15" t="s">
         <v>27</v>
+      </c>
+      <c r="M15" t="s">
+        <v>40</v>
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
@@ -10037,13 +10202,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F16" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="I16" t="s">
         <v>120</v>
-      </c>
-      <c r="I16" t="s">
-        <v>121</v>
       </c>
       <c r="K16" t="s">
         <v>45</v>
@@ -10081,7 +10246,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="F17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G17" t="s">
         <v>77</v>
@@ -10126,7 +10291,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G18" t="s">
         <v>29</v>
@@ -10136,6 +10301,9 @@
       </c>
       <c r="K18" t="s">
         <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>33</v>
       </c>
       <c r="O18">
         <f t="shared" si="0"/>
@@ -10171,7 +10339,7 @@
         <v>0.59</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
         <v>35</v>
@@ -10215,7 +10383,7 @@
         <v>1.01</v>
       </c>
       <c r="F20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G20" t="s">
         <v>60</v>
@@ -10225,6 +10393,9 @@
       </c>
       <c r="K20" t="s">
         <v>32</v>
+      </c>
+      <c r="M20" t="s">
+        <v>40</v>
       </c>
       <c r="O20">
         <f t="shared" si="0"/>
@@ -10260,7 +10431,7 @@
         <v>1.02</v>
       </c>
       <c r="F21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G21" t="s">
         <v>77</v>
@@ -10305,7 +10476,7 @@
         <v>1.03</v>
       </c>
       <c r="F22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>107</v>
@@ -10315,6 +10486,9 @@
       </c>
       <c r="K22" t="s">
         <v>32</v>
+      </c>
+      <c r="M22" t="s">
+        <v>40</v>
       </c>
       <c r="O22">
         <f t="shared" si="0"/>
@@ -10350,7 +10524,7 @@
         <v>1.05</v>
       </c>
       <c r="F23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G23" t="s">
         <v>67</v>
@@ -10360,6 +10534,9 @@
       </c>
       <c r="K23" t="s">
         <v>32</v>
+      </c>
+      <c r="M23" t="s">
+        <v>40</v>
       </c>
       <c r="O23">
         <f t="shared" si="0"/>
@@ -10394,7 +10571,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="F24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>107</v>
@@ -10404,6 +10581,9 @@
       </c>
       <c r="K24" t="s">
         <v>32</v>
+      </c>
+      <c r="M24" t="s">
+        <v>40</v>
       </c>
       <c r="O24">
         <f t="shared" si="0"/>
@@ -10439,7 +10619,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="F25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G25" t="s">
         <v>80</v>
@@ -14853,11 +15033,11 @@
         <v>-10</v>
       </c>
       <c r="Q194">
-        <f t="shared" ref="Q194:Q225" si="38">P194-O194</f>
+        <f t="shared" ref="Q194:Q200" si="38">P194-O194</f>
         <v>0</v>
       </c>
       <c r="R194" t="str">
-        <f t="shared" ref="R194:R225" si="39">IF(Q194=0,"&lt;1 second","&lt;"&amp;(ROUND(Q194,2)+1)&amp;" seconds")</f>
+        <f t="shared" ref="R194:R200" si="39">IF(Q194=0,"&lt;1 second","&lt;"&amp;(ROUND(Q194,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S194">
@@ -15027,13 +15207,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select primary input method" sqref="K2 K3 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 K52 K53 K54 K55 K56 K57 K58 K59 K60 K61 K62 K63 K64 K65 K66 K67 K68 K69 K70 K71 K72 K73 K74 K75 K76 K77 K78 K79 K80 K81 K82 K83 K84 K85 K86 K87 K88 K89 K90 K91 K92 K93 K94 K95 K96 K97 K98 K99 K100 K101 K102 K103 K104 K105 K106 K107 K108 K109 K110 K111 K112 K113 K114 K115 K116 K117 K118 K119 K120 K121 K122 K123 K124 K125 K126 K127 K128 K129 K130 K131 K132 K133 K134 K135 K136 K137 K138 K139 K140 K141 K142 K143 K144 K145 K146 K147 K148 K149 K150 K151 K152 K153 K154 K155 K156 K157 K158 K159 K160 K161 K162 K163 K164 K165 K166 K167 K168 K169 K170 K171 K172 K173 K174 K175 K176 K177 K178 K179 K180 K181 K182 K183 K184 K185 K186 K187 K188 K189 K190 K191 K192 K193 K194 K195 K196 K197 K198 K199 K200" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select primary input method" sqref="K2:K200" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"cursor,keyboard,gesture,complex gesture,multi_step,multi_input"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select secondary input method" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88 L89 L90 L91 L92 L93 L94 L95 L96 L97 L98 L99 L100 L101 L102 L103 L104 L105 L106 L107 L108 L109 L110 L111 L112 L113 L114 L115 L116 L117 L118 L119 L120 L121 L122 L123 L124 L125 L126 L127 L128 L129 L130 L131 L132 L133 L134 L135 L136 L137 L138 L139 L140 L141 L142 L143 L144 L145 L146 L147 L148 L149 L150 L151 L152 L153 L154 L155 L156 L157 L158 L159 L160 L161 L162 L163 L164 L165 L166 L167 L168 L169 L170 L171 L172 L173 L174 L175 L176 L177 L178 L179 L180 L181 L182 L183 L184 L185 L186 L187 L188 L189 L190 L191 L192 L193 L194 L195 L196 L197 L198 L199 L200" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select secondary input method" sqref="L2:L200" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"cursor,keyboard,gesture,complex gesture,multi_step,multi_input"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select location" sqref="M2 M3 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 M52 M53 M54 M55 M56 M57 M58 M59 M60 M61 M62 M63 M64 M65 M66 M67 M68 M69 M70 M71 M72 M73 M74 M75 M76 M77 M78 M79 M80 M81 M82 M83 M84 M85 M86 M87 M88 M89 M90 M91 M92 M93 M94 M95 M96 M97 M98 M99 M100 M101 M102 M103 M104 M105 M106 M107 M108 M109 M110 M111 M112 M113 M114 M115 M116 M117 M118 M119 M120 M121 M122 M123 M124 M125 M126 M127 M128 M129 M130 M131 M132 M133 M134 M135 M136 M137 M138 M139 M140 M141 M142 M143 M144 M145 M146 M147 M148 M149 M150 M151 M152 M153 M154 M155 M156 M157 M158 M159 M160 M161 M162 M163 M164 M165 M166 M167 M168 M169 M170 M171 M172 M173 M174 M175 M176 M177 M178 M179 M180 M181 M182 M183 M184 M185 M186 M187 M188 M189 M190 M191 M192 M193 M194 M195 M196 M197 M198 M199 M200" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select location" sqref="M2:M200" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"canvas,gui"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15043,21 +15223,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385E0E9D-94D8-564F-846C-A105F247DA61}">
-  <dimension ref="A1:U200"/>
+  <dimension ref="A1:U201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
     <col min="2" max="2" width="6.1640625" customWidth="1"/>
     <col min="3" max="3" width="7.33203125" customWidth="1"/>
     <col min="4" max="4" width="5.33203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="46.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="64.1640625" customWidth="1"/>
     <col min="8" max="8" width="33" customWidth="1"/>
     <col min="9" max="9" width="26.83203125" customWidth="1"/>
     <col min="10" max="10" width="13.33203125" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="8.1640625" customWidth="1"/>
+    <col min="13" max="13" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30.33203125" customWidth="1"/>
     <col min="15" max="15" width="13.33203125" customWidth="1"/>
     <col min="16" max="16" width="12.6640625" customWidth="1"/>
@@ -15135,6 +15315,28 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>10.36</v>
+      </c>
+      <c r="E2" s="4">
+        <f>D2</f>
+        <v>10.36</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" t="s">
+        <v>62</v>
+      </c>
       <c r="O2">
         <f t="shared" ref="O2:P33" si="0">(INT(D2)*60+(D2-INT(D2))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
         <v>0</v>
@@ -15144,30 +15346,43 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <f t="shared" ref="Q2:Q65" si="1">P2-O2</f>
+        <f t="shared" ref="Q2:Q66" si="1">P2-O2</f>
         <v>0</v>
       </c>
       <c r="R2" t="str">
-        <f t="shared" ref="R2:R65" si="2">IF(Q2=0,"&lt;1 second","&lt;"&amp;(ROUND(Q2,2)+1)&amp;" seconds")</f>
+        <f t="shared" ref="R2:R66" si="2">IF(Q2=0,"&lt;1 second","&lt;"&amp;(ROUND(Q2,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S2">
-        <f t="shared" ref="S2:S65" si="3">Q2+1</f>
+        <f>Q2+1</f>
         <v>1</v>
       </c>
       <c r="T2">
-        <f t="shared" ref="T2:T65" si="4">Q2+0.5</f>
+        <f t="shared" ref="T2:T66" si="3">Q2+0.5</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D3" s="4">
+        <v>10.37</v>
+      </c>
+      <c r="E3" s="4">
+        <f t="shared" ref="E3:E35" si="4">D3</f>
+        <v>10.37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" t="s">
+        <v>62</v>
+      </c>
       <c r="O3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999999988631</v>
       </c>
       <c r="P3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999999988631</v>
       </c>
       <c r="Q3">
         <f t="shared" si="1"/>
@@ -15178,22 +15393,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S3">
+        <f t="shared" ref="S2:S66" si="5">Q3+1</f>
+        <v>1</v>
+      </c>
+      <c r="T3">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D4" s="4">
+        <v>10.37</v>
+      </c>
+      <c r="E4" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+        <v>10.37</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>171</v>
+      </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999999988631</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999999988631</v>
       </c>
       <c r="Q4">
         <f t="shared" si="1"/>
@@ -15204,22 +15432,38 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S4">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T4">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D5" s="4">
+        <v>10.37</v>
+      </c>
+      <c r="E5" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+        <v>10.37</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M5" t="s">
+        <v>158</v>
+      </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999999988631</v>
       </c>
       <c r="P5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999999988631</v>
       </c>
       <c r="Q5">
         <f t="shared" si="1"/>
@@ -15230,22 +15474,38 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T5">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D6" s="4">
+        <v>10.38</v>
+      </c>
+      <c r="E6" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+        <v>10.38</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="I6" t="s">
+        <v>101</v>
+      </c>
+      <c r="M6" t="s">
+        <v>158</v>
+      </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.0000000000001137</v>
       </c>
       <c r="P6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.0000000000001137</v>
       </c>
       <c r="Q6">
         <f t="shared" si="1"/>
@@ -15256,48 +15516,79 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D7" s="4">
+        <v>10.38</v>
+      </c>
+      <c r="E7" s="4">
+        <v>10.4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>148</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="I7" t="s">
+        <v>170</v>
+      </c>
+      <c r="M7" t="s">
+        <v>158</v>
+      </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.0000000000001137</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.9999999999998863</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;3 seconds</v>
       </c>
       <c r="S7">
+        <f t="shared" si="5"/>
+        <v>2.9999999999998863</v>
+      </c>
+      <c r="T7">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T7">
+        <v>2.4999999999998863</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D8" s="4">
+        <v>10.41</v>
+      </c>
+      <c r="E8" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+        <v>10.41</v>
+      </c>
+      <c r="G8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" t="s">
+        <v>62</v>
+      </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <f t="shared" si="1"/>
@@ -15308,22 +15599,41 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T8">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D9" s="4">
+        <v>10.41</v>
+      </c>
+      <c r="E9" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+        <v>10.41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="I9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" t="s">
+        <v>158</v>
+      </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <f t="shared" si="1"/>
@@ -15334,48 +15644,72 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S9">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T9">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D10" s="4">
+        <v>10.42</v>
+      </c>
+      <c r="E10" s="4">
+        <v>10.44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;3 seconds</v>
       </c>
       <c r="S10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="T10">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D11" s="4">
+        <v>10.44</v>
+      </c>
+      <c r="E11" s="4">
+        <v>10.44</v>
+      </c>
+      <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
+        <v>62</v>
+      </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <f t="shared" si="1"/>
@@ -15386,22 +15720,34 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S11">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T11">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D12" s="4">
+        <v>10.45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>10.45</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" t="s">
+        <v>62</v>
+      </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.9999999999998863</v>
       </c>
       <c r="P12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.9999999999998863</v>
       </c>
       <c r="Q12">
         <f t="shared" si="1"/>
@@ -15412,22 +15758,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S12">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T12">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D13" s="4">
+        <v>10.46</v>
+      </c>
+      <c r="E13" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+        <v>10.46</v>
+      </c>
+      <c r="G13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10.000000000000114</v>
       </c>
       <c r="P13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10.000000000000114</v>
       </c>
       <c r="Q13">
         <f t="shared" si="1"/>
@@ -15438,74 +15797,114 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S13">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D14" s="4">
+        <v>10.48</v>
+      </c>
+      <c r="E14" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="14" t="s">
+        <v>151</v>
+      </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;3 seconds</v>
       </c>
       <c r="S14">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="T14">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D15" s="4">
+        <v>10.51</v>
+      </c>
+      <c r="E15" s="4">
+        <v>10.52</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" t="s">
+        <v>26</v>
+      </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S15">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="T15">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T15">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D16" s="4">
+        <v>10.52</v>
+      </c>
+      <c r="E16" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+        <v>10.52</v>
+      </c>
+      <c r="G16" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q16">
         <f t="shared" si="1"/>
@@ -15516,22 +15915,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S16">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T16">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D17" s="4">
+        <v>10.53</v>
+      </c>
+      <c r="E17" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="15:20" x14ac:dyDescent="0.2">
+        <v>10.53</v>
+      </c>
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s">
+        <v>26</v>
+      </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.999999999999886</v>
       </c>
       <c r="P17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.999999999999886</v>
       </c>
       <c r="Q17">
         <f t="shared" si="1"/>
@@ -15542,48 +15954,73 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S17">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T17">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D18" s="4">
+        <v>10.53</v>
+      </c>
+      <c r="E18" s="4">
+        <v>10.55</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" t="s">
+        <v>62</v>
+      </c>
       <c r="O18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.999999999999886</v>
       </c>
       <c r="P18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19.000000000000114</v>
       </c>
       <c r="Q18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.0000000000002274</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;3 seconds</v>
       </c>
       <c r="S18">
+        <f t="shared" si="5"/>
+        <v>3.0000000000002274</v>
+      </c>
+      <c r="T18">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T18">
+        <v>2.5000000000002274</v>
+      </c>
+    </row>
+    <row r="19" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D19" s="4">
+        <v>10.55</v>
+      </c>
+      <c r="E19" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="15:20" x14ac:dyDescent="0.2">
+        <v>10.55</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="I19" t="s">
+        <v>26</v>
+      </c>
       <c r="O19">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19.000000000000114</v>
       </c>
       <c r="P19">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19.000000000000114</v>
       </c>
       <c r="Q19">
         <f t="shared" si="1"/>
@@ -15594,22 +16031,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S19">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T19">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D20" s="4">
+        <v>10.57</v>
+      </c>
+      <c r="E20" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="15:20" x14ac:dyDescent="0.2">
+        <v>10.57</v>
+      </c>
+      <c r="G20" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
       <c r="O20">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P20">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q20">
         <f t="shared" si="1"/>
@@ -15620,22 +16070,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S20">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T20">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D21" s="4">
+        <v>10.58</v>
+      </c>
+      <c r="E21" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="15:20" x14ac:dyDescent="0.2">
+        <v>10.58</v>
+      </c>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" t="s">
+        <v>59</v>
+      </c>
       <c r="O21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q21">
         <f t="shared" si="1"/>
@@ -15646,22 +16109,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S21">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T21">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D22" s="4">
+        <v>10.58</v>
+      </c>
+      <c r="E22" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="15:20" x14ac:dyDescent="0.2">
+        <v>10.58</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" t="s">
+        <v>53</v>
+      </c>
       <c r="O22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q22">
         <f t="shared" si="1"/>
@@ -15672,74 +16148,114 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S22">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T22">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D23" s="4">
+        <v>10.58</v>
+      </c>
+      <c r="E23" s="4">
+        <v>10.59</v>
+      </c>
+      <c r="F23" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" t="s">
+        <v>53</v>
+      </c>
       <c r="O23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S23">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="T23">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="15:20" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="24" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D24" s="4">
+        <v>10.59</v>
+      </c>
+      <c r="E24" s="4">
+        <v>11</v>
+      </c>
+      <c r="G24" t="s">
+        <v>149</v>
+      </c>
+      <c r="I24" t="s">
+        <v>76</v>
+      </c>
       <c r="O24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="P24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S24">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="T24">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T24">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D25" s="4">
+        <v>11</v>
+      </c>
+      <c r="E25" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="G25" t="s">
+        <v>152</v>
+      </c>
+      <c r="I25" t="s">
+        <v>26</v>
+      </c>
       <c r="O25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q25">
         <f t="shared" si="1"/>
@@ -15750,48 +16266,74 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S25">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T25">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T25">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D26" s="4">
+        <v>11.02</v>
+      </c>
+      <c r="E26" s="4">
+        <v>11.03</v>
+      </c>
+      <c r="G26" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
       <c r="O26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="P26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26.999999999999886</v>
       </c>
       <c r="Q26">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.99999999999988631</v>
       </c>
       <c r="R26" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S26">
+        <f t="shared" si="5"/>
+        <v>1.9999999999998863</v>
+      </c>
+      <c r="T26">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T26">
+        <v>1.4999999999998863</v>
+      </c>
+    </row>
+    <row r="27" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D27" s="4">
+        <v>11.04</v>
+      </c>
+      <c r="E27" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11.04</v>
+      </c>
+      <c r="F27" s="15"/>
+      <c r="G27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" t="s">
+        <v>62</v>
+      </c>
       <c r="O27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27.999999999999886</v>
       </c>
       <c r="P27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27.999999999999886</v>
       </c>
       <c r="Q27">
         <f t="shared" si="1"/>
@@ -15802,22 +16344,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S27">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T27">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D28" s="4">
+        <v>11.04</v>
+      </c>
+      <c r="E28" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11.04</v>
+      </c>
+      <c r="G28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28" t="s">
+        <v>26</v>
+      </c>
       <c r="O28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27.999999999999886</v>
       </c>
       <c r="P28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27.999999999999886</v>
       </c>
       <c r="Q28">
         <f t="shared" si="1"/>
@@ -15828,22 +16383,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S28">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T28">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T28">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D29" s="4">
+        <v>11.05</v>
+      </c>
+      <c r="E29" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11.05</v>
+      </c>
+      <c r="G29" t="s">
+        <v>138</v>
+      </c>
+      <c r="I29" t="s">
+        <v>62</v>
+      </c>
       <c r="O29">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29.000000000000114</v>
       </c>
       <c r="P29">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29.000000000000114</v>
       </c>
       <c r="Q29">
         <f t="shared" si="1"/>
@@ -15854,22 +16422,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S29">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T29">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T29">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D30" s="4">
+        <v>11.06</v>
+      </c>
+      <c r="E30" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11.06</v>
+      </c>
+      <c r="G30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30" t="s">
+        <v>26</v>
+      </c>
       <c r="O30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q30">
         <f t="shared" si="1"/>
@@ -15880,22 +16461,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S30">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T30">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D31" s="4">
+        <v>11.06</v>
+      </c>
+      <c r="E31" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11.06</v>
+      </c>
+      <c r="G31" t="s">
+        <v>154</v>
+      </c>
+      <c r="I31" t="s">
+        <v>53</v>
+      </c>
       <c r="O31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q31">
         <f t="shared" si="1"/>
@@ -15906,22 +16500,36 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S31">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T31">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T31">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="4:20" ht="16" x14ac:dyDescent="0.2">
+      <c r="D32" s="4">
+        <v>11.07</v>
+      </c>
+      <c r="E32" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11.07</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" t="s">
+        <v>80</v>
+      </c>
+      <c r="I32" t="s">
+        <v>62</v>
+      </c>
       <c r="O32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q32">
         <f t="shared" si="1"/>
@@ -15932,22 +16540,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S32">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T32">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T32">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D33" s="4">
+        <v>11.07</v>
+      </c>
+      <c r="E33" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11.07</v>
+      </c>
+      <c r="G33" t="s">
+        <v>67</v>
+      </c>
+      <c r="I33" t="s">
+        <v>62</v>
+      </c>
       <c r="O33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q33">
         <f t="shared" si="1"/>
@@ -15958,22 +16579,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S33">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T33">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T33">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D34" s="4">
+        <v>11.08</v>
+      </c>
+      <c r="E34" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="34" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11.08</v>
+      </c>
+      <c r="G34" t="s">
+        <v>146</v>
+      </c>
+      <c r="I34" t="s">
+        <v>85</v>
+      </c>
       <c r="O34">
-        <f t="shared" ref="O34:P65" si="5">(INT(D34)*60+(D34-INT(D34))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
-        <v>0</v>
+        <f t="shared" ref="O34:P66" si="6">(INT(D34)*60+(D34-INT(D34))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
+        <v>32</v>
       </c>
       <c r="P34">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>32</v>
       </c>
       <c r="Q34">
         <f t="shared" si="1"/>
@@ -15984,22 +16618,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T34">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T34">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D35" s="4">
+        <v>11.09</v>
+      </c>
+      <c r="E35" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="35" spans="15:20" x14ac:dyDescent="0.2">
+        <v>11.09</v>
+      </c>
+      <c r="G35" t="s">
+        <v>153</v>
+      </c>
+      <c r="I35" t="s">
+        <v>26</v>
+      </c>
       <c r="O35">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>33</v>
       </c>
       <c r="P35">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>33</v>
       </c>
       <c r="Q35">
         <f t="shared" si="1"/>
@@ -16010,48 +16657,73 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S35">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T35">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T35">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D36" s="4">
+        <v>11.09</v>
+      </c>
+      <c r="E36" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36" t="s">
+        <v>87</v>
+      </c>
       <c r="O36">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>33</v>
       </c>
       <c r="P36">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="Q36">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S36">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="T36">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T36">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="37" spans="15:20" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="37" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D37" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="E37" s="4">
+        <f>D37</f>
+        <v>11.1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>119</v>
+      </c>
+      <c r="I37" t="s">
+        <v>120</v>
+      </c>
       <c r="O37">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="P37">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="Q37">
         <f t="shared" si="1"/>
@@ -16062,22 +16734,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S37">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T37">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T37">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="38" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D38" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="E38" s="4">
+        <f>D38</f>
+        <v>11.1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38" t="s">
+        <v>26</v>
+      </c>
       <c r="O38">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="P38">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="Q38">
         <f t="shared" si="1"/>
@@ -16088,22 +16773,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S38">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T38">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T38">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="39" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D39" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="E39" s="4">
+        <f t="shared" ref="E39:E67" si="7">D39</f>
+        <v>11.1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>80</v>
+      </c>
+      <c r="I39" t="s">
+        <v>62</v>
+      </c>
       <c r="O39">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="P39">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="Q39">
         <f t="shared" si="1"/>
@@ -16114,22 +16812,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S39">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T39">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T39">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="40" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D40" s="4">
+        <v>11.11</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" si="7"/>
+        <v>11.11</v>
+      </c>
+      <c r="G40" t="s">
+        <v>67</v>
+      </c>
+      <c r="I40" t="s">
+        <v>62</v>
+      </c>
       <c r="O40">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>35</v>
       </c>
       <c r="P40">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>35</v>
       </c>
       <c r="Q40">
         <f t="shared" si="1"/>
@@ -16140,48 +16851,73 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S40">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T40">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T40">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="41" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D41" s="4">
+        <v>11.12</v>
+      </c>
+      <c r="E41" s="4">
+        <v>11.13</v>
+      </c>
+      <c r="G41" t="s">
+        <v>139</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>171</v>
+      </c>
       <c r="O41">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>35.999999999999886</v>
       </c>
       <c r="P41">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>37.000000000000114</v>
       </c>
       <c r="Q41">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0000000000002274</v>
       </c>
       <c r="R41" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S41">
+        <f t="shared" si="5"/>
+        <v>2.0000000000002274</v>
+      </c>
+      <c r="T41">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T41">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="42" spans="15:20" x14ac:dyDescent="0.2">
+        <v>1.5000000000002274</v>
+      </c>
+    </row>
+    <row r="42" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D42" s="4">
+        <v>11.14</v>
+      </c>
+      <c r="E42" s="4">
+        <f t="shared" si="7"/>
+        <v>11.14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>63</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>171</v>
+      </c>
       <c r="O42">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>38</v>
       </c>
       <c r="P42">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>38</v>
       </c>
       <c r="Q42">
         <f t="shared" si="1"/>
@@ -16192,22 +16928,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S42">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T42">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T42">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="43" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D43" s="4">
+        <v>11.15</v>
+      </c>
+      <c r="E43" s="4">
+        <f t="shared" si="7"/>
+        <v>11.15</v>
+      </c>
+      <c r="G43" t="s">
+        <v>153</v>
+      </c>
+      <c r="I43" t="s">
+        <v>26</v>
+      </c>
       <c r="O43">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>39</v>
       </c>
       <c r="P43">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>39</v>
       </c>
       <c r="Q43">
         <f t="shared" si="1"/>
@@ -16218,22 +16967,41 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S43">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T43">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T43">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="44" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D44" s="4">
+        <v>11.15</v>
+      </c>
+      <c r="E44" s="4">
+        <f t="shared" si="7"/>
+        <v>11.15</v>
+      </c>
+      <c r="F44" t="s">
+        <v>160</v>
+      </c>
+      <c r="G44" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" t="s">
+        <v>101</v>
+      </c>
+      <c r="N44" t="s">
+        <v>161</v>
+      </c>
       <c r="O44">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>39</v>
       </c>
       <c r="P44">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>39</v>
       </c>
       <c r="Q44">
         <f t="shared" si="1"/>
@@ -16244,22 +17012,41 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S44">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T44">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T44">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="45" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D45" s="4">
+        <v>11.16</v>
+      </c>
+      <c r="E45" s="4">
+        <f t="shared" si="7"/>
+        <v>11.16</v>
+      </c>
+      <c r="F45" t="s">
+        <v>141</v>
+      </c>
+      <c r="G45" t="s">
+        <v>75</v>
+      </c>
+      <c r="I45" t="s">
+        <v>101</v>
+      </c>
+      <c r="N45" t="s">
+        <v>161</v>
+      </c>
       <c r="O45">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="P45">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="Q45">
         <f t="shared" si="1"/>
@@ -16270,22 +17057,41 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S45">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T45">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T45">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="46" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D46" s="4">
+        <v>11.17</v>
+      </c>
+      <c r="E46" s="4">
+        <f t="shared" si="7"/>
+        <v>11.17</v>
+      </c>
+      <c r="F46" t="s">
+        <v>162</v>
+      </c>
+      <c r="G46" t="s">
+        <v>75</v>
+      </c>
+      <c r="I46" t="s">
+        <v>101</v>
+      </c>
+      <c r="N46" t="s">
+        <v>161</v>
+      </c>
       <c r="O46">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>41</v>
       </c>
       <c r="P46">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>41</v>
       </c>
       <c r="Q46">
         <f t="shared" si="1"/>
@@ -16296,22 +17102,38 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S46">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T46">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T46">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="47" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D47" s="4">
+        <v>11.18</v>
+      </c>
+      <c r="E47" s="4">
+        <f t="shared" si="7"/>
+        <v>11.18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>49</v>
+      </c>
+      <c r="I47" t="s">
+        <v>87</v>
+      </c>
+      <c r="N47" t="s">
+        <v>88</v>
+      </c>
       <c r="O47">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>42</v>
       </c>
       <c r="P47">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>42</v>
       </c>
       <c r="Q47">
         <f t="shared" si="1"/>
@@ -16322,22 +17144,38 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S47">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T47">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T47">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="48" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D48" s="4">
+        <v>11.19</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="7"/>
+        <v>11.19</v>
+      </c>
+      <c r="G48" t="s">
+        <v>49</v>
+      </c>
+      <c r="I48" t="s">
+        <v>87</v>
+      </c>
+      <c r="N48" t="s">
+        <v>88</v>
+      </c>
       <c r="O48">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>43</v>
       </c>
       <c r="P48">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>43</v>
       </c>
       <c r="Q48">
         <f t="shared" si="1"/>
@@ -16348,22 +17186,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S48">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T48">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T48">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="49" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D49" s="4">
+        <v>11.2</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="7"/>
+        <v>11.2</v>
+      </c>
+      <c r="G49" t="s">
+        <v>80</v>
+      </c>
+      <c r="I49" t="s">
+        <v>62</v>
+      </c>
       <c r="O49">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>43.999999999999886</v>
       </c>
       <c r="P49">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>43.999999999999886</v>
       </c>
       <c r="Q49">
         <f t="shared" si="1"/>
@@ -16374,22 +17225,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S49">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T49">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T49">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="50" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D50" s="4">
+        <v>11.2</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" si="7"/>
+        <v>11.2</v>
+      </c>
+      <c r="G50" t="s">
+        <v>67</v>
+      </c>
+      <c r="I50" t="s">
+        <v>62</v>
+      </c>
       <c r="O50">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>43.999999999999886</v>
       </c>
       <c r="P50">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>43.999999999999886</v>
       </c>
       <c r="Q50">
         <f t="shared" si="1"/>
@@ -16400,48 +17264,76 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S50">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T50">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T50">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="51" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D51" s="4">
+        <v>11.2</v>
+      </c>
+      <c r="E51" s="4">
+        <v>11.21</v>
+      </c>
+      <c r="G51" t="s">
+        <v>60</v>
+      </c>
+      <c r="I51" t="s">
+        <v>53</v>
+      </c>
       <c r="O51">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>43.999999999999886</v>
       </c>
       <c r="P51">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>45.000000000000114</v>
       </c>
       <c r="Q51">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0000000000002274</v>
       </c>
       <c r="R51" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S51">
+        <f t="shared" si="5"/>
+        <v>2.0000000000002274</v>
+      </c>
+      <c r="T51">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T51">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="52" spans="15:20" x14ac:dyDescent="0.2">
+        <v>1.5000000000002274</v>
+      </c>
+    </row>
+    <row r="52" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D52" s="4">
+        <v>11.21</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" si="7"/>
+        <v>11.21</v>
+      </c>
+      <c r="F52" t="s">
+        <v>143</v>
+      </c>
+      <c r="G52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52" t="s">
+        <v>26</v>
+      </c>
       <c r="O52">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>45.000000000000114</v>
       </c>
       <c r="P52">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>45.000000000000114</v>
       </c>
       <c r="Q52">
         <f t="shared" si="1"/>
@@ -16452,22 +17344,35 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S52">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T52">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T52">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="53" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D53" s="4">
+        <v>11.22</v>
+      </c>
+      <c r="E53" s="4">
+        <f t="shared" si="7"/>
+        <v>11.22</v>
+      </c>
+      <c r="G53" t="s">
+        <v>67</v>
+      </c>
+      <c r="I53" t="s">
+        <v>62</v>
+      </c>
       <c r="O53">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>46.000000000000114</v>
       </c>
       <c r="P53">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>46.000000000000114</v>
       </c>
       <c r="Q53">
         <f t="shared" si="1"/>
@@ -16478,22 +17383,38 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S53">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T53">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T53">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="54" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D54" s="4">
+        <v>11.23</v>
+      </c>
+      <c r="E54" s="4">
+        <f t="shared" si="7"/>
+        <v>11.23</v>
+      </c>
+      <c r="F54" t="s">
+        <v>164</v>
+      </c>
+      <c r="G54" t="s">
+        <v>63</v>
+      </c>
+      <c r="I54" t="s">
+        <v>64</v>
+      </c>
       <c r="O54">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>47</v>
       </c>
       <c r="P54">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>47</v>
       </c>
       <c r="Q54">
         <f t="shared" si="1"/>
@@ -16504,22 +17425,38 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S54">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T54">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T54">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="55" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D55" s="4">
+        <v>11.23</v>
+      </c>
+      <c r="E55" s="4">
+        <f t="shared" si="7"/>
+        <v>11.23</v>
+      </c>
+      <c r="F55" t="s">
+        <v>165</v>
+      </c>
+      <c r="G55" t="s">
+        <v>117</v>
+      </c>
+      <c r="I55" t="s">
+        <v>26</v>
+      </c>
       <c r="O55">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>47</v>
       </c>
       <c r="P55">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>47</v>
       </c>
       <c r="Q55">
         <f t="shared" si="1"/>
@@ -16530,22 +17467,41 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S55">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T55">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T55">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="56" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D56" s="4">
+        <v>11.24</v>
+      </c>
+      <c r="E56" s="4">
+        <f t="shared" si="7"/>
+        <v>11.24</v>
+      </c>
+      <c r="F56" t="s">
+        <v>166</v>
+      </c>
+      <c r="G56" t="s">
+        <v>46</v>
+      </c>
+      <c r="I56" t="s">
+        <v>101</v>
+      </c>
+      <c r="N56" t="s">
+        <v>161</v>
+      </c>
       <c r="O56">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>48</v>
       </c>
       <c r="P56">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>48</v>
       </c>
       <c r="Q56">
         <f t="shared" si="1"/>
@@ -16556,74 +17512,129 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S56">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T56">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T56">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="57" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D57" s="4">
+        <v>11.24</v>
+      </c>
+      <c r="E57" s="4">
+        <v>11.25</v>
+      </c>
+      <c r="F57" t="s">
+        <v>141</v>
+      </c>
+      <c r="G57" t="s">
+        <v>75</v>
+      </c>
+      <c r="I57" t="s">
+        <v>101</v>
+      </c>
+      <c r="N57" t="s">
+        <v>161</v>
+      </c>
       <c r="O57">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>48</v>
       </c>
       <c r="P57">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>49</v>
       </c>
       <c r="Q57">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S57">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="T57">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T57">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="58" spans="15:20" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="58" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D58" s="4">
+        <v>11.25</v>
+      </c>
+      <c r="E58" s="4">
+        <v>11.26</v>
+      </c>
+      <c r="F58" t="s">
+        <v>167</v>
+      </c>
+      <c r="G58" t="s">
+        <v>75</v>
+      </c>
+      <c r="I58" t="s">
+        <v>101</v>
+      </c>
+      <c r="N58" t="s">
+        <v>161</v>
+      </c>
       <c r="O58">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>49</v>
       </c>
       <c r="P58">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>50</v>
       </c>
       <c r="Q58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S58">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="T58">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T58">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="59" spans="15:20" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="59" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D59" s="4">
+        <v>11.27</v>
+      </c>
+      <c r="E59" s="4">
+        <f t="shared" si="7"/>
+        <v>11.27</v>
+      </c>
+      <c r="F59" t="s">
+        <v>168</v>
+      </c>
+      <c r="G59" t="s">
+        <v>46</v>
+      </c>
+      <c r="I59" t="s">
+        <v>87</v>
+      </c>
+      <c r="N59" t="s">
+        <v>88</v>
+      </c>
       <c r="O59">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="P59">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="Q59">
         <f t="shared" si="1"/>
@@ -16634,48 +17645,79 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S59">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T59">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T59">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="60" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D60" s="4">
+        <v>11.27</v>
+      </c>
+      <c r="E60" s="4">
+        <v>11.28</v>
+      </c>
+      <c r="F60" t="s">
+        <v>169</v>
+      </c>
+      <c r="G60" t="s">
+        <v>46</v>
+      </c>
+      <c r="I60" t="s">
+        <v>87</v>
+      </c>
+      <c r="N60" t="s">
+        <v>88</v>
+      </c>
       <c r="O60">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="P60">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>51.999999999999886</v>
       </c>
       <c r="Q60">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.99999999999988631</v>
       </c>
       <c r="R60" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S60">
+        <f t="shared" si="5"/>
+        <v>1.9999999999998863</v>
+      </c>
+      <c r="T60">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T60">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="61" spans="15:20" x14ac:dyDescent="0.2">
+        <v>1.4999999999998863</v>
+      </c>
+    </row>
+    <row r="61" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D61" s="4">
+        <v>11.29</v>
+      </c>
+      <c r="E61" s="4">
+        <f t="shared" si="7"/>
+        <v>11.29</v>
+      </c>
+      <c r="F61" t="s">
+        <v>144</v>
+      </c>
+      <c r="G61" t="s">
+        <v>68</v>
+      </c>
       <c r="O61">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>52.999999999999886</v>
       </c>
       <c r="P61">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>52.999999999999886</v>
       </c>
       <c r="Q61">
         <f t="shared" si="1"/>
@@ -16686,48 +17728,79 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S61">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T61">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T61">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="62" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D62" s="4">
+        <v>11.3</v>
+      </c>
+      <c r="E62" s="4">
+        <v>11.31</v>
+      </c>
+      <c r="F62" t="s">
+        <v>145</v>
+      </c>
+      <c r="G62" t="s">
+        <v>52</v>
+      </c>
+      <c r="I62" t="s">
+        <v>53</v>
+      </c>
       <c r="O62">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>54.000000000000114</v>
       </c>
       <c r="P62">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>55</v>
       </c>
       <c r="Q62">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.99999999999988631</v>
       </c>
       <c r="R62" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S62">
+        <f t="shared" si="5"/>
+        <v>1.9999999999998863</v>
+      </c>
+      <c r="T62">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T62">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="63" spans="15:20" x14ac:dyDescent="0.2">
+        <v>1.4999999999998863</v>
+      </c>
+    </row>
+    <row r="63" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D63" s="4">
+        <v>11.32</v>
+      </c>
+      <c r="E63" s="4">
+        <f t="shared" si="7"/>
+        <v>11.32</v>
+      </c>
+      <c r="F63" t="s">
+        <v>142</v>
+      </c>
+      <c r="G63" t="s">
+        <v>67</v>
+      </c>
+      <c r="I63" t="s">
+        <v>62</v>
+      </c>
       <c r="O63">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>56</v>
       </c>
       <c r="P63">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>56</v>
       </c>
       <c r="Q63">
         <f t="shared" si="1"/>
@@ -16738,22 +17811,41 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S63">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T63">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T63">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="64" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D64" s="4">
+        <v>11.33</v>
+      </c>
+      <c r="E64" s="4">
+        <f t="shared" si="7"/>
+        <v>11.33</v>
+      </c>
+      <c r="F64" t="s">
+        <v>140</v>
+      </c>
+      <c r="G64" t="s">
+        <v>46</v>
+      </c>
+      <c r="I64" t="s">
+        <v>101</v>
+      </c>
+      <c r="N64" t="s">
+        <v>161</v>
+      </c>
       <c r="O64">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>57</v>
       </c>
       <c r="P64">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>57</v>
       </c>
       <c r="Q64">
         <f t="shared" si="1"/>
@@ -16764,3565 +17856,3653 @@
         <v>&lt;1 second</v>
       </c>
       <c r="S64">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="T64">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T64">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="65" spans="15:20" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D65" s="4">
+        <v>11.34</v>
+      </c>
+      <c r="E65" s="4">
+        <v>11.35</v>
+      </c>
+      <c r="F65" t="s">
+        <v>141</v>
+      </c>
+      <c r="G65" t="s">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s">
+        <v>101</v>
+      </c>
+      <c r="N65" t="s">
+        <v>161</v>
+      </c>
       <c r="O65">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>58</v>
       </c>
       <c r="P65">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>59</v>
       </c>
       <c r="Q65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;1 second</v>
+        <v>&lt;2 seconds</v>
       </c>
       <c r="S65">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="T65">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T65">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="66" spans="15:20" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="66" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D66" s="4">
+        <v>11.35</v>
+      </c>
+      <c r="E66" s="4">
+        <f t="shared" si="7"/>
+        <v>11.35</v>
+      </c>
+      <c r="F66" t="s">
+        <v>167</v>
+      </c>
+      <c r="G66" t="s">
+        <v>75</v>
+      </c>
+      <c r="I66" t="s">
+        <v>101</v>
+      </c>
+      <c r="N66" t="s">
+        <v>161</v>
+      </c>
       <c r="O66">
-        <f t="shared" ref="O66:P97" si="6">(INT(D66)*60+(D66-INT(D66))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>59</v>
       </c>
       <c r="P66">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="Q66">
-        <f t="shared" ref="Q66:Q129" si="7">P66-O66</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R66" t="str">
-        <f t="shared" ref="R66:R129" si="8">IF(Q66=0,"&lt;1 second","&lt;"&amp;(ROUND(Q66,2)+1)&amp;" seconds")</f>
+        <f t="shared" si="2"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S66">
-        <f t="shared" ref="S66:S129" si="9">Q66+1</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="T66">
-        <f t="shared" ref="T66:T129" si="10">Q66+0.5</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="67" spans="15:20" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="D67" s="4">
+        <v>11.36</v>
+      </c>
+      <c r="E67" s="4">
+        <f t="shared" si="7"/>
+        <v>11.36</v>
+      </c>
+      <c r="F67" t="s">
+        <v>168</v>
+      </c>
+      <c r="G67" t="s">
+        <v>46</v>
+      </c>
+      <c r="I67" t="s">
+        <v>101</v>
+      </c>
+      <c r="N67" t="s">
+        <v>88</v>
+      </c>
       <c r="O67">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ref="O67:P98" si="8">(INT(D67)*60+(D67-INT(D67))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
+        <v>60</v>
       </c>
       <c r="P67">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>60</v>
       </c>
       <c r="Q67">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="Q67:Q130" si="9">P67-O67</f>
         <v>0</v>
       </c>
       <c r="R67" t="str">
+        <f t="shared" ref="R67:R130" si="10">IF(Q67=0,"&lt;1 second","&lt;"&amp;(ROUND(Q67,2)+1)&amp;" seconds")</f>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S67">
+        <f t="shared" ref="S67:S130" si="11">Q67+1</f>
+        <v>1</v>
+      </c>
+      <c r="T67">
+        <f t="shared" ref="T67:T130" si="12">Q67+0.5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="68" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O68">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S67">
+        <v>-636</v>
+      </c>
+      <c r="P68">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q68">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="R68" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="68" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O68">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R68" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S68">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T68">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="69" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O69">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S68">
+        <v>-636</v>
+      </c>
+      <c r="P69">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q69">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="R69" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="69" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O69">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R69" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S69">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T69">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O70">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S69">
+        <v>-636</v>
+      </c>
+      <c r="P70">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q70">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="R70" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="70" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O70">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R70" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S70">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T70">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O71">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S70">
+        <v>-636</v>
+      </c>
+      <c r="P71">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q71">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="R71" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="71" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O71">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R71" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S71">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T71">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="72" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O72">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S71">
+        <v>-636</v>
+      </c>
+      <c r="P72">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q72">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="R72" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="72" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O72">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R72" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S72">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T72">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="73" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O73">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S72">
+        <v>-636</v>
+      </c>
+      <c r="P73">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q73">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="R73" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="73" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O73">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R73" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S73">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T73">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="74" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O74">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S73">
+        <v>-636</v>
+      </c>
+      <c r="P74">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q74">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="R74" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="74" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O74">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R74" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S74">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T74">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="75" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O75">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S74">
+        <v>-636</v>
+      </c>
+      <c r="P75">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q75">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="R75" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="75" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O75">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R75" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S75">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T75">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="76" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O76">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S75">
+        <v>-636</v>
+      </c>
+      <c r="P76">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q76">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="R76" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="76" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R76" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S76">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T76">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="77" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O77">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S76">
+        <v>-636</v>
+      </c>
+      <c r="P77">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q77">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="R77" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="77" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O77">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R77" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S77">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T77">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="78" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O78">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S77">
+        <v>-636</v>
+      </c>
+      <c r="P78">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q78">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="R78" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="78" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O78">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R78" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S78">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T78">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="79" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O79">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S78">
+        <v>-636</v>
+      </c>
+      <c r="P79">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q79">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="R79" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="79" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O79">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q79">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R79" t="str">
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S79">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T79">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="80" spans="4:20" x14ac:dyDescent="0.2">
+      <c r="O80">
         <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S79">
+        <v>-636</v>
+      </c>
+      <c r="P80">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q80">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="R80" t="str">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="80" spans="15:20" x14ac:dyDescent="0.2">
-      <c r="O80">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R80" t="str">
-        <f t="shared" si="8"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S80">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T80">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O81">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P81">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R81" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="82" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O82">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P82">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R82" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T82">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="83" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O83">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P83">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R83" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="84" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O84">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P84">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="85" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O85">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P85">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R85" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="86" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O86">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P86">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R86" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S86">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T86">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="87" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O87">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P87">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R87" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S87">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T87">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="88" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O88">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P88">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R88" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S88">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T88">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="89" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O89">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P89">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R89" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T89">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="90" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O90">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P90">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R90" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="91" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O91">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P91">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q91">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R91" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="92" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O92">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P92">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q92">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R92" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S92">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T92">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="93" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O93">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P93">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R93" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S93">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T93">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="94" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O94">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P94">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q94">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R94" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S94">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T94">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="95" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O95">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P95">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R95" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="96" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O96">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P96">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R96" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S96">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T96">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="97" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O97">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P97">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="Q97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R97" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S97">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T97">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="98" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O98">
-        <f t="shared" ref="O98:P129" si="11">(INT(D98)*60+(D98-INT(D98))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-636</v>
       </c>
       <c r="P98">
+        <f t="shared" si="8"/>
+        <v>-636</v>
+      </c>
+      <c r="Q98">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R98" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S98">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R98" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S98">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T98">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="99" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O99">
+        <f t="shared" ref="O99:P130" si="13">(INT(D99)*60+(D99-INT(D99))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
+        <v>-636</v>
+      </c>
+      <c r="P99">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q99">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R99" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S99">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P99">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R99" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S99">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T99">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="100" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O100">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P100">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q100">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R100" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S100">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P100">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R100" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S100">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T100">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="101" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O101">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P101">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q101">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R101" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S101">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R101" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S101">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T101">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="102" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O102">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P102">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q102">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R102" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S102">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q102">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R102" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S102">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T102">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="103" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O103">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P103">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q103">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R103" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S103">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q103">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R103" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S103">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T103">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="104" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O104">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P104">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R104" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S104">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R104" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S104">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="105" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O105">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P105">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q105">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R105" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S105">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q105">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R105" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S105">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="106" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O106">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P106">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q106">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R106" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S106">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P106">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q106">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R106" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S106">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T106">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="107" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O107">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P107">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q107">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R107" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S107">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P107">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q107">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R107" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S107">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T107">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="108" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O108">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P108">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q108">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R108" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S108">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P108">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R108" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S108">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T108">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="109" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O109">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P109">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q109">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R109" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S109">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P109">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q109">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R109" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S109">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T109">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="110" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O110">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P110">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q110">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R110" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S110">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q110">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R110" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S110">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T110">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="111" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O111">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P111">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q111">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R111" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S111">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P111">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q111">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R111" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S111">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T111">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="112" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O112">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P112">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q112">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R112" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S112">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R112" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S112">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T112">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="113" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O113">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P113">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q113">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R113" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S113">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P113">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R113" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S113">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T113">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="114" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O114">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P114">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q114">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R114" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S114">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R114" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S114">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T114">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="115" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O115">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P115">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q115">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R115" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S115">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R115" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S115">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T115">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="116" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O116">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P116">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q116">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R116" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S116">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R116" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S116">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T116">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="117" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O117">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P117">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q117">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R117" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S117">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q117">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R117" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S117">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T117">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="118" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O118">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P118">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q118">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R118" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S118">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R118" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S118">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T118">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="119" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O119">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P119">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q119">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R119" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S119">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R119" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S119">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T119">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="120" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O120">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P120">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q120">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R120" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S120">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R120" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S120">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T120">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="121" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O121">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P121">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q121">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R121" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S121">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P121">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q121">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R121" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S121">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T121">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="122" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O122">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P122">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q122">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R122" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S122">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R122" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S122">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T122">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="123" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O123">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P123">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q123">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R123" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S123">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R123" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S123">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T123">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="124" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O124">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P124">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q124">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R124" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S124">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R124" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S124">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T124">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="125" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O125">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P125">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q125">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R125" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S125">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R125" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S125">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T125">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="126" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O126">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P126">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q126">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R126" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S126">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R126" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S126">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T126">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="127" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O127">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P127">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q127">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R127" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S127">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R127" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S127">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T127">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="128" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O128">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P128">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q128">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R128" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S128">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R128" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S128">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T128">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="129" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O129">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="P129">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R129" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S129">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R129" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S129">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="T129">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="130" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O130">
-        <f t="shared" ref="O130:P161" si="12">(INT(D130)*60+(D130-INT(D130))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>-636</v>
       </c>
       <c r="P130">
+        <f t="shared" si="13"/>
+        <v>-636</v>
+      </c>
+      <c r="Q130">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R130" t="str">
+        <f t="shared" si="10"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S130">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="T130">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <f t="shared" ref="Q130:Q193" si="13">P130-O130</f>
-        <v>0</v>
-      </c>
-      <c r="R130" t="str">
-        <f t="shared" ref="R130:R193" si="14">IF(Q130=0,"&lt;1 second","&lt;"&amp;(ROUND(Q130,2)+1)&amp;" seconds")</f>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S130">
-        <f t="shared" ref="S130:S193" si="15">Q130+1</f>
-        <v>1</v>
-      </c>
-      <c r="T130">
-        <f t="shared" ref="T130:T193" si="16">Q130+0.5</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="131" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O131">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" ref="O131:P162" si="14">(INT(D131)*60+(D131-INT(D131))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
+        <v>-636</v>
       </c>
       <c r="P131">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q131">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="Q131:Q194" si="15">P131-O131</f>
         <v>0</v>
       </c>
       <c r="R131" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="R131:R194" si="16">IF(Q131=0,"&lt;1 second","&lt;"&amp;(ROUND(Q131,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S131">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="S131:S194" si="17">Q131+1</f>
         <v>1</v>
       </c>
       <c r="T131">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="T131:T194" si="18">Q131+0.5</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="132" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O132">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P132">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q132">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R132" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S132">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T132">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="133" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O133">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P133">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q133">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R133" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S133">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T133">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="134" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O134">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P134">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q134">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R134" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S134">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T134">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="135" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O135">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P135">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q135">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R135" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S135">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T135">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="136" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O136">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P136">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q136">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R136" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S136">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T136">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="137" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O137">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P137">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q137">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R137" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S137">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T137">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="138" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O138">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P138">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q138">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R138" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S138">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T138">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="139" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O139">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P139">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q139">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R139" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S139">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T139">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="140" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O140">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P140">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q140">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R140" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S140">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T140">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="141" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O141">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P141">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q141">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R141" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S141">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T141">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="142" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O142">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P142">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q142">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R142" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S142">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T142">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="143" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O143">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P143">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q143">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R143" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S143">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T143">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="144" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O144">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P144">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q144">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R144" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S144">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T144">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="145" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O145">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P145">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q145">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R145" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S145">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T145">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="146" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O146">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P146">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q146">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R146" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S146">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T146">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="147" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O147">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P147">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q147">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R147" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S147">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T147">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="148" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O148">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P148">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q148">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R148" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S148">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T148">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="149" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O149">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P149">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q149">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R149" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S149">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T149">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="150" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O150">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P150">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q150">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R150" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S150">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T150">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="151" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O151">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P151">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q151">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R151" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S151">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T151">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="152" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O152">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P152">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q152">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R152" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S152">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T152">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="153" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O153">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P153">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q153">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R153" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S153">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T153">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="154" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O154">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P154">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q154">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R154" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S154">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T154">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="155" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O155">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P155">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q155">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R155" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S155">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T155">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="156" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O156">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P156">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R156" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S156">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T156">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="157" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O157">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P157">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q157">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R157" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S157">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T157">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="158" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O158">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P158">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q158">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R158" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S158">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T158">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="159" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O159">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P159">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q159">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R159" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S159">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T159">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="160" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O160">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P160">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q160">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R160" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S160">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="161" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O161">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P161">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="Q161">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R161" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S161">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="T161">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="162" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O162">
-        <f t="shared" ref="O162:P193" si="17">(INT(D162)*60+(D162-INT(D162))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>-636</v>
       </c>
       <c r="P162">
+        <f t="shared" si="14"/>
+        <v>-636</v>
+      </c>
+      <c r="Q162">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R162" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S162">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q162">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R162" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S162">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T162">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="163" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O163">
+        <f t="shared" ref="O163:P194" si="19">(INT(D163)*60+(D163-INT(D163))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
+        <v>-636</v>
+      </c>
+      <c r="P163">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q163">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R163" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S163">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P163">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q163">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R163" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S163">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T163">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="164" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O164">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P164">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q164">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R164" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S164">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P164">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q164">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R164" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S164">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T164">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="165" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O165">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P165">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q165">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R165" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S165">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P165">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q165">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R165" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S165">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T165">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="166" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O166">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P166">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q166">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R166" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S166">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P166">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q166">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R166" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S166">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T166">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="167" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O167">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P167">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q167">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R167" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S167">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P167">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q167">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R167" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S167">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T167">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="168" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O168">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P168">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q168">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R168" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S168">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P168">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q168">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R168" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S168">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T168">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="169" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O169">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P169">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q169">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R169" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S169">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P169">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q169">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R169" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S169">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T169">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="170" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O170">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P170">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q170">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R170" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S170">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P170">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q170">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R170" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S170">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T170">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="171" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O171">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P171">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q171">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R171" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S171">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P171">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q171">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R171" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S171">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T171">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="172" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O172">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P172">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q172">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R172" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S172">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P172">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q172">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R172" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S172">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T172">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="173" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O173">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P173">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q173">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R173" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S173">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P173">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q173">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R173" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S173">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T173">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="174" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O174">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P174">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q174">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R174" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S174">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P174">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q174">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R174" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S174">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T174">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="175" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O175">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P175">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q175">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R175" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S175">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P175">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q175">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R175" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S175">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T175">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="176" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O176">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P176">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q176">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R176" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S176">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P176">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q176">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R176" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S176">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T176">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="177" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O177">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P177">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q177">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R177" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S177">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P177">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q177">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R177" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S177">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T177">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="178" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O178">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P178">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q178">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R178" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S178">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P178">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q178">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R178" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S178">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T178">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="179" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O179">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P179">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q179">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R179" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S179">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P179">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q179">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R179" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S179">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T179">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="180" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O180">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P180">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q180">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R180" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S180">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P180">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q180">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R180" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S180">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T180">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="181" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O181">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P181">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q181">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R181" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S181">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P181">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q181">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R181" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S181">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T181">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="182" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O182">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P182">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q182">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R182" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S182">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P182">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q182">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R182" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S182">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T182">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="183" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O183">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P183">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q183">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R183" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S183">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P183">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q183">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R183" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S183">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T183">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="184" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O184">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P184">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q184">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R184" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S184">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P184">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q184">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R184" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S184">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T184">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="185" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O185">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P185">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q185">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R185" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S185">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P185">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q185">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R185" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S185">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T185">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="186" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O186">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P186">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q186">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R186" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S186">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P186">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q186">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R186" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S186">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T186">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="187" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O187">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P187">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q187">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R187" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S187">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P187">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q187">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R187" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S187">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T187">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="188" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O188">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P188">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q188">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R188" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S188">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P188">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q188">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R188" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S188">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T188">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="189" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O189">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P189">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q189">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R189" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S189">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P189">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q189">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R189" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S189">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T189">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="190" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O190">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P190">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q190">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R190" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S190">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P190">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q190">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R190" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S190">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T190">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="191" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O191">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P191">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q191">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R191" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S191">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P191">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q191">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R191" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S191">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T191">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="192" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O192">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P192">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q192">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R192" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S192">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P192">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q192">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R192" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S192">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T192">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="193" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O193">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="P193">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q193">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R193" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S193">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P193">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Q193">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R193" t="str">
-        <f t="shared" si="14"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S193">
-        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="T193">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="194" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O194">
-        <f t="shared" ref="O194:P200" si="18">(INT(D194)*60+(D194-INT(D194))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
-        <v>0</v>
+        <f t="shared" si="19"/>
+        <v>-636</v>
       </c>
       <c r="P194">
+        <f t="shared" si="19"/>
+        <v>-636</v>
+      </c>
+      <c r="Q194">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R194" t="str">
+        <f t="shared" si="16"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S194">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="T194">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q194">
-        <f t="shared" ref="Q194:Q200" si="19">P194-O194</f>
-        <v>0</v>
-      </c>
-      <c r="R194" t="str">
-        <f t="shared" ref="R194:R200" si="20">IF(Q194=0,"&lt;1 second","&lt;"&amp;(ROUND(Q194,2)+1)&amp;" seconds")</f>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S194">
-        <f t="shared" ref="S194:S200" si="21">Q194+1</f>
-        <v>1</v>
-      </c>
-      <c r="T194">
-        <f t="shared" ref="T194:T200" si="22">Q194+0.5</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="195" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O195">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" ref="O195:P201" si="20">(INT(D195)*60+(D195-INT(D195))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
+        <v>-636</v>
       </c>
       <c r="P195">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="Q195">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="Q195:Q201" si="21">P195-O195</f>
         <v>0</v>
       </c>
       <c r="R195" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="R195:R201" si="22">IF(Q195=0,"&lt;1 second","&lt;"&amp;(ROUND(Q195,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S195">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="S195:S201" si="23">Q195+1</f>
         <v>1</v>
       </c>
       <c r="T195">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="T195:T201" si="24">Q195+0.5</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="196" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O196">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="P196">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="Q196">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R196" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S196">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="T196">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="197" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O197">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="P197">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="Q197">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R197" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S197">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="T197">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="198" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O198">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="P198">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="Q198">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R198" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S198">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="T198">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="199" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O199">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="P199">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="Q199">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R199" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>&lt;1 second</v>
       </c>
       <c r="S199">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="T199">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="200" spans="15:20" x14ac:dyDescent="0.2">
       <c r="O200">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="P200">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-636</v>
       </c>
       <c r="Q200">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R200" t="str">
+        <f t="shared" si="22"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S200">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="T200">
+        <f t="shared" si="24"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="201" spans="15:20" x14ac:dyDescent="0.2">
+      <c r="O201">
         <f t="shared" si="20"/>
-        <v>&lt;1 second</v>
-      </c>
-      <c r="S200">
+        <v>-636</v>
+      </c>
+      <c r="P201">
+        <f t="shared" si="20"/>
+        <v>-636</v>
+      </c>
+      <c r="Q201">
         <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="T200">
+        <v>0</v>
+      </c>
+      <c r="R201" t="str">
         <f t="shared" si="22"/>
+        <v>&lt;1 second</v>
+      </c>
+      <c r="S201">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="T201">
+        <f t="shared" si="24"/>
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select location" sqref="M2:M200" xr:uid="{4A07B43F-7A47-EA46-8F4B-8C55F58F53EB}">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select location" sqref="M186:M201" xr:uid="{4A07B43F-7A47-EA46-8F4B-8C55F58F53EB}">
       <formula1>"canvas,gui"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select secondary input method" sqref="L2:L200" xr:uid="{36F435CC-D902-8749-9E43-E8688C09CAD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select secondary input method" sqref="L2:L201" xr:uid="{36F435CC-D902-8749-9E43-E8688C09CAD0}">
       <formula1>"cursor,keyboard,gesture,complex gesture,multi_step,multi_input"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select primary input method" sqref="K2:K200" xr:uid="{744635E9-F70E-D44C-806B-E63BC471D5A9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select primary input method" sqref="K2:K201" xr:uid="{744635E9-F70E-D44C-806B-E63BC471D5A9}">
       <formula1>"cursor,keyboard,gesture,complex gesture,multi_step,multi_input"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select difficulty rating" sqref="H2:H200" xr:uid="{01D0EF21-0709-914F-81A0-337809055DE5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select difficulty rating" sqref="H2:H201" xr:uid="{01D0EF21-0709-914F-81A0-337809055DE5}">
       <formula1>"EASY,MEDIUM,HARD,VERY HARD"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M185" xr:uid="{AB9CB58A-88E0-514D-B8EC-054981FB52D8}">
+      <formula1>"gui, canvas, layers panel"</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{78D73091-4804-1B44-A896-11D5EE575F9D}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -20331,25 +21511,25 @@
           <x14:formula1>
             <xm:f>_lists!$C$2:$C$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>N2:N200</xm:sqref>
+          <xm:sqref>N2:N201</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select a secondary tag" xr:uid="{C11373A2-7D2E-9543-B19C-E73A9FCF5FC5}">
           <x14:formula1>
             <xm:f>_lists!$B$2:$B$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J200</xm:sqref>
+          <xm:sqref>J2:J201</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select a primary tag" xr:uid="{AFFA4EE7-185F-0842-B389-1EBD06BF88A9}">
           <x14:formula1>
             <xm:f>_lists!$B$2:$B$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I200</xm:sqref>
+          <xm:sqref>I2:I201</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please select from the list or leave blank." promptTitle="Select value" prompt="Select or type an action" xr:uid="{F1980560-6D9D-7847-9293-ACABDE791133}">
           <x14:formula1>
             <xm:f>_lists!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G200</xm:sqref>
+          <xm:sqref>G2:G201</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -20359,7 +21539,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="64" customWidth="1"/>
@@ -20368,13 +21548,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" t="s">
         <v>131</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>132</v>
-      </c>
-      <c r="C1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -20417,8 +21597,8 @@
       <c r="B5" t="s">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
-        <v>90</v>
+      <c r="C5" s="14" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -20516,6 +21696,9 @@
       <c r="B14" t="s">
         <v>31</v>
       </c>
+      <c r="C14" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -20554,18 +21737,24 @@
         <v>49</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>75</v>
       </c>
+      <c r="B20" s="14" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>70</v>
       </c>
+      <c r="B21" s="14" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
@@ -20579,7 +21768,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -20618,18 +21807,83 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>115</v>
+      <c r="A32" s="14" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" s="14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" s="14" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/Research/Workflow Analysis/Workflow_Analysis.xlsx
+++ b/Research/Workflow Analysis/Workflow_Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marci/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marci/Desktop/Creative-Visual-Design-Accessibility-Tools/Research/Workflow Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DD1C54-8B1E-6D41-A8B9-9B5DC6F95A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A5392E-C85A-D749-B612-83585A8546D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="760" windowWidth="29400" windowHeight="17340" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17340" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TEMPLATE" sheetId="1" r:id="rId1"/>
@@ -443,11 +443,6 @@
     <t>the hardest part of this action is that it is multistep and requires scrolling which is frustrating with voice</t>
   </si>
   <si>
-    <t xml:space="preserve">
-ASMR UI Designing in FIGMA - STRIPE - No Talking | Silent
-ASMR UI Designing in FIGMA - STRIPE - No Talking | Silent</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=OLb7Rqo1KVQ</t>
   </si>
   <si>
@@ -1115,6 +1110,9 @@
   </si>
   <si>
     <t>[hover] over [reference(s)] on [canvas]</t>
+  </si>
+  <si>
+    <t>ASMR UI Designing in FIGMA - STRIPE - No Talking | Silent</t>
   </si>
 </sst>
 </file>
@@ -6683,11 +6681,11 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <f t="shared" ref="Q194:Q225" si="38">P194-O194</f>
+        <f t="shared" ref="Q194:Q200" si="38">P194-O194</f>
         <v>0</v>
       </c>
       <c r="R194" t="str">
-        <f t="shared" ref="R194:R225" si="39">IF(Q194=0,"&lt;1 second","&lt;"&amp;(ROUND(Q194,2)+1)&amp;" seconds")</f>
+        <f t="shared" ref="R194:R200" si="39">IF(Q194=0,"&lt;1 second","&lt;"&amp;(ROUND(Q194,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S194">
@@ -6968,13 +6966,13 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" t="s">
         <v>333</v>
-      </c>
-      <c r="C2" t="s">
-        <v>334</v>
       </c>
       <c r="D2" s="3">
         <v>55.48</v>
@@ -6983,7 +6981,7 @@
         <v>55.54</v>
       </c>
       <c r="F2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G2" t="s">
         <v>85</v>
@@ -7322,13 +7320,13 @@
         <v>56.05</v>
       </c>
       <c r="G9" t="s">
+        <v>226</v>
+      </c>
+      <c r="I9" t="s">
         <v>227</v>
       </c>
-      <c r="I9" t="s">
-        <v>228</v>
-      </c>
       <c r="J9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K9" t="s">
         <v>43</v>
@@ -7465,7 +7463,7 @@
         <v>56.2</v>
       </c>
       <c r="F12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G12" t="s">
         <v>99</v>
@@ -7611,7 +7609,7 @@
         <v>56.29</v>
       </c>
       <c r="F15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G15" t="s">
         <v>85</v>
@@ -7757,7 +7755,7 @@
         <v>56.35</v>
       </c>
       <c r="F18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G18" t="s">
         <v>45</v>
@@ -7807,7 +7805,7 @@
         <v>56.38</v>
       </c>
       <c r="F19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G19" t="s">
         <v>50</v>
@@ -7858,7 +7856,7 @@
         <v>56.39</v>
       </c>
       <c r="G20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I20" t="s">
         <v>29</v>
@@ -7952,7 +7950,7 @@
         <v>56.48</v>
       </c>
       <c r="G22" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I22" t="s">
         <v>29</v>
@@ -8306,13 +8304,13 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" t="s">
         <v>340</v>
-      </c>
-      <c r="C2" t="s">
-        <v>341</v>
       </c>
       <c r="D2" s="3">
         <v>57</v>
@@ -8321,13 +8319,13 @@
         <v>57.02</v>
       </c>
       <c r="G2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I2" t="s">
         <v>46</v>
       </c>
       <c r="J2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K2" t="s">
         <v>92</v>
@@ -8371,13 +8369,13 @@
         <v>57.03</v>
       </c>
       <c r="G3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I3" t="s">
         <v>46</v>
       </c>
       <c r="J3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K3" t="s">
         <v>92</v>
@@ -8472,7 +8470,7 @@
         <v>57.06</v>
       </c>
       <c r="F5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G5" t="s">
         <v>32</v>
@@ -8522,7 +8520,7 @@
         <v>57.1</v>
       </c>
       <c r="F6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G6" t="s">
         <v>32</v>
@@ -8572,16 +8570,16 @@
         <v>57.11</v>
       </c>
       <c r="F7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I7" t="s">
         <v>77</v>
       </c>
       <c r="J7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K7" t="s">
         <v>92</v>
@@ -8622,7 +8620,7 @@
         <v>57.12</v>
       </c>
       <c r="G8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I8" t="s">
         <v>29</v>
@@ -8718,13 +8716,13 @@
         <v>57.13</v>
       </c>
       <c r="G10" t="s">
+        <v>226</v>
+      </c>
+      <c r="I10" t="s">
         <v>227</v>
       </c>
-      <c r="I10" t="s">
-        <v>228</v>
-      </c>
       <c r="J10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K10" t="s">
         <v>43</v>
@@ -8813,7 +8811,7 @@
         <v>57.17</v>
       </c>
       <c r="F12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G12" t="s">
         <v>82</v>
@@ -8863,7 +8861,7 @@
         <v>57.2</v>
       </c>
       <c r="F13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
@@ -8913,13 +8911,13 @@
         <v>57.22</v>
       </c>
       <c r="G14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I14" t="s">
         <v>46</v>
       </c>
       <c r="J14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K14" t="s">
         <v>92</v>
@@ -9058,7 +9056,7 @@
         <v>57.26</v>
       </c>
       <c r="F17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
@@ -9108,7 +9106,7 @@
         <v>57.47</v>
       </c>
       <c r="F18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G18" t="s">
         <v>32</v>
@@ -9159,7 +9157,7 @@
         <v>57.51</v>
       </c>
       <c r="G19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I19" t="s">
         <v>29</v>
@@ -9255,7 +9253,7 @@
         <v>57.51</v>
       </c>
       <c r="G21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I21" t="s">
         <v>74</v>
@@ -9302,7 +9300,7 @@
         <v>57.56</v>
       </c>
       <c r="F22" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G22" t="s">
         <v>32</v>
@@ -9353,7 +9351,7 @@
         <v>57.57</v>
       </c>
       <c r="G23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I23" t="s">
         <v>29</v>
@@ -9449,7 +9447,7 @@
         <v>58.02</v>
       </c>
       <c r="G25" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I25" t="s">
         <v>74</v>
@@ -9760,7 +9758,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -9807,10 +9805,10 @@
         <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -9832,7 +9830,7 @@
         <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -9854,7 +9852,7 @@
         <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -9876,7 +9874,7 @@
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -9887,7 +9885,7 @@
         <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -9906,7 +9904,7 @@
         <v>117</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" t="s">
         <v>97</v>
@@ -9914,13 +9912,13 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s">
         <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -9928,10 +9926,10 @@
         <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C16" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -9939,7 +9937,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
         <v>25</v>
@@ -9958,21 +9956,21 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C20" t="s">
         <v>74</v>
@@ -9980,10 +9978,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C21" t="s">
         <v>112</v>
@@ -9991,7 +9989,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s">
         <v>96</v>
@@ -10002,7 +10000,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s">
         <v>77</v>
@@ -10013,7 +10011,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
         <v>115</v>
@@ -10030,18 +10028,18 @@
         <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -10049,7 +10047,7 @@
         <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C27" t="s">
         <v>42</v>
@@ -10057,18 +10055,18 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B28" t="s">
         <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B29" t="s">
         <v>42</v>
@@ -10079,7 +10077,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B30" t="s">
         <v>29</v>
@@ -10093,7 +10091,7 @@
         <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C31" t="s">
         <v>101</v>
@@ -10112,7 +10110,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
         <v>52</v>
@@ -10120,7 +10118,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C34" t="s">
         <v>72</v>
@@ -10128,7 +10126,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C35" t="s">
         <v>26</v>
@@ -10136,15 +10134,15 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C37" t="s">
         <v>84</v>
@@ -10152,15 +10150,15 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C39" t="s">
         <v>126</v>
@@ -10168,7 +10166,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C40" t="s">
         <v>118</v>
@@ -10176,7 +10174,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C41" t="s">
         <v>111</v>
@@ -10184,31 +10182,31 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C43" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C45" t="s">
         <v>59</v>
@@ -10216,17 +10214,17 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
@@ -10246,32 +10244,32 @@
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
@@ -10291,7 +10289,7 @@
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
@@ -12269,11 +12267,11 @@
         <v>40</v>
       </c>
       <c r="Q34">
-        <f t="shared" ref="Q34:Q65" si="8">P34-O34</f>
+        <f t="shared" ref="Q34:Q52" si="8">P34-O34</f>
         <v>0</v>
       </c>
       <c r="R34" t="str">
-        <f t="shared" ref="R34:R65" si="9">IF(Q34=0,"&lt;1 second","&lt;"&amp;(ROUND(Q34,2)+1)&amp;" seconds")</f>
+        <f t="shared" ref="R34:R52" si="9">IF(Q34=0,"&lt;1 second","&lt;"&amp;(ROUND(Q34,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S34" s="3">
@@ -13734,13 +13732,13 @@
     </row>
     <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" t="s">
         <v>133</v>
-      </c>
-      <c r="C2" t="s">
-        <v>134</v>
       </c>
       <c r="D2" s="3">
         <v>0.1</v>
@@ -13749,7 +13747,7 @@
         <v>0.13</v>
       </c>
       <c r="F2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G2" t="s">
         <v>45</v>
@@ -13802,7 +13800,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="F3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>32</v>
@@ -13855,7 +13853,7 @@
         <v>0.15</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>32</v>
@@ -13873,7 +13871,7 @@
         <v>35</v>
       </c>
       <c r="N4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
@@ -13908,7 +13906,7 @@
         <v>0.2</v>
       </c>
       <c r="F5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>32</v>
@@ -13926,7 +13924,7 @@
         <v>35</v>
       </c>
       <c r="N5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
@@ -13961,7 +13959,7 @@
         <v>0.23</v>
       </c>
       <c r="F6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G6" t="s">
         <v>56</v>
@@ -13979,7 +13977,7 @@
         <v>28</v>
       </c>
       <c r="N6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
@@ -14014,16 +14012,16 @@
         <v>0.26</v>
       </c>
       <c r="F7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>143</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>144</v>
       </c>
       <c r="I7" t="s">
         <v>77</v>
       </c>
       <c r="J7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K7" t="s">
         <v>27</v>
@@ -14032,7 +14030,7 @@
         <v>28</v>
       </c>
       <c r="N7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
@@ -14067,16 +14065,16 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="F8" t="s">
+        <v>146</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>147</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="I8" t="s">
         <v>83</v>
       </c>
       <c r="J8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K8" t="s">
         <v>27</v>
@@ -14085,7 +14083,7 @@
         <v>28</v>
       </c>
       <c r="N8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
@@ -14120,16 +14118,16 @@
         <v>0.31</v>
       </c>
       <c r="F9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I9" t="s">
         <v>83</v>
       </c>
       <c r="J9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K9" t="s">
         <v>27</v>
@@ -14138,7 +14136,7 @@
         <v>28</v>
       </c>
       <c r="N9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
@@ -14211,16 +14209,16 @@
         <v>0.39</v>
       </c>
       <c r="F11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="I11" t="s">
         <v>153</v>
       </c>
-      <c r="I11" t="s">
-        <v>154</v>
-      </c>
       <c r="J11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K11" t="s">
         <v>27</v>
@@ -14229,7 +14227,7 @@
         <v>28</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
@@ -14264,16 +14262,16 @@
         <v>0.46</v>
       </c>
       <c r="F12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G12" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" t="s">
         <v>153</v>
       </c>
-      <c r="I12" t="s">
-        <v>154</v>
-      </c>
       <c r="J12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K12" t="s">
         <v>27</v>
@@ -14282,7 +14280,7 @@
         <v>28</v>
       </c>
       <c r="N12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
@@ -14318,16 +14316,16 @@
         <v>0.47</v>
       </c>
       <c r="F13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I13" t="s">
         <v>77</v>
       </c>
       <c r="J13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K13" t="s">
         <v>27</v>
@@ -14336,7 +14334,7 @@
         <v>28</v>
       </c>
       <c r="N13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
@@ -14371,16 +14369,16 @@
         <v>0.5</v>
       </c>
       <c r="F14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>159</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>160</v>
       </c>
       <c r="I14" t="s">
         <v>46</v>
       </c>
       <c r="J14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K14" t="s">
         <v>92</v>
@@ -14425,16 +14423,16 @@
         <v>0.51</v>
       </c>
       <c r="F15" t="s">
+        <v>161</v>
+      </c>
+      <c r="G15" t="s">
         <v>162</v>
-      </c>
-      <c r="G15" t="s">
-        <v>163</v>
       </c>
       <c r="I15" t="s">
         <v>46</v>
       </c>
       <c r="J15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K15" t="s">
         <v>92</v>
@@ -14478,16 +14476,16 @@
         <v>0.54</v>
       </c>
       <c r="F16" t="s">
+        <v>164</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>165</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>166</v>
       </c>
       <c r="I16" t="s">
         <v>46</v>
       </c>
       <c r="J16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K16" t="s">
         <v>92</v>
@@ -14532,7 +14530,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>41</v>
@@ -14585,16 +14583,16 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="F18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I18" t="s">
         <v>46</v>
       </c>
       <c r="J18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K18" t="s">
         <v>92</v>
@@ -14639,7 +14637,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>32</v>
@@ -14693,7 +14691,7 @@
         <v>0.59</v>
       </c>
       <c r="F20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G20" t="s">
         <v>45</v>
@@ -14746,16 +14744,16 @@
         <v>1.01</v>
       </c>
       <c r="F21" t="s">
+        <v>170</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>171</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>172</v>
       </c>
       <c r="I21" t="s">
         <v>57</v>
       </c>
       <c r="J21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
         <v>27</v>
@@ -14764,7 +14762,7 @@
         <v>28</v>
       </c>
       <c r="N21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O21">
         <f t="shared" si="0"/>
@@ -14800,16 +14798,16 @@
         <v>1.02</v>
       </c>
       <c r="F22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I22" t="s">
         <v>46</v>
       </c>
       <c r="J22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K22" t="s">
         <v>92</v>
@@ -14854,16 +14852,16 @@
         <v>1.03</v>
       </c>
       <c r="F23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I23" t="s">
         <v>83</v>
       </c>
       <c r="J23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K23" t="s">
         <v>27</v>
@@ -14872,7 +14870,7 @@
         <v>28</v>
       </c>
       <c r="N23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O23">
         <f t="shared" si="0"/>
@@ -14908,7 +14906,7 @@
         <v>1.05</v>
       </c>
       <c r="F24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G24" t="s">
         <v>51</v>
@@ -14961,16 +14959,16 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="F25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I25" t="s">
         <v>83</v>
       </c>
       <c r="J25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K25" t="s">
         <v>27</v>
@@ -14979,7 +14977,7 @@
         <v>28</v>
       </c>
       <c r="N25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O25">
         <f t="shared" si="0"/>
@@ -15015,7 +15013,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="F26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G26" t="s">
         <v>24</v>
@@ -15033,7 +15031,7 @@
         <v>28</v>
       </c>
       <c r="N26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O26">
         <f t="shared" si="0"/>
@@ -15284,13 +15282,13 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" t="s">
         <v>182</v>
-      </c>
-      <c r="C2" t="s">
-        <v>183</v>
       </c>
       <c r="D2" s="3">
         <v>10.36</v>
@@ -15402,13 +15400,13 @@
         <v>10.37</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -15417,7 +15415,7 @@
         <v>28</v>
       </c>
       <c r="N4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
@@ -15504,7 +15502,7 @@
         <v>10.38</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I6" t="s">
         <v>29</v>
@@ -15554,16 +15552,16 @@
         <v>10.4</v>
       </c>
       <c r="F7" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="I7" t="s">
         <v>189</v>
       </c>
-      <c r="I7" t="s">
-        <v>190</v>
-      </c>
       <c r="J7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K7" t="s">
         <v>119</v>
@@ -15572,7 +15570,7 @@
         <v>66</v>
       </c>
       <c r="N7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
@@ -15659,10 +15657,10 @@
         <v>10.41</v>
       </c>
       <c r="F9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I9" t="s">
         <v>29</v>
@@ -15863,13 +15861,13 @@
         <v>10.46</v>
       </c>
       <c r="G13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I13" t="s">
         <v>46</v>
       </c>
       <c r="J13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K13" t="s">
         <v>92</v>
@@ -15928,7 +15926,7 @@
         <v>35</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
@@ -15963,13 +15961,13 @@
         <v>10.52</v>
       </c>
       <c r="G15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I15" t="s">
         <v>46</v>
       </c>
       <c r="J15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K15" t="s">
         <v>92</v>
@@ -16014,13 +16012,13 @@
         <v>10.52</v>
       </c>
       <c r="G16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I16" t="s">
         <v>46</v>
       </c>
       <c r="J16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K16" t="s">
         <v>92</v>
@@ -16065,13 +16063,13 @@
         <v>10.53</v>
       </c>
       <c r="G17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I17" t="s">
         <v>46</v>
       </c>
       <c r="J17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K17" t="s">
         <v>92</v>
@@ -16166,13 +16164,13 @@
         <v>10.55</v>
       </c>
       <c r="G19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I19" t="s">
         <v>46</v>
       </c>
       <c r="J19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K19" t="s">
         <v>92</v>
@@ -16217,13 +16215,13 @@
         <v>10.57</v>
       </c>
       <c r="G20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I20" t="s">
         <v>46</v>
       </c>
       <c r="J20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K20" t="s">
         <v>92</v>
@@ -16283,7 +16281,7 @@
         <v>28</v>
       </c>
       <c r="N21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O21">
         <f t="shared" si="0"/>
@@ -16369,16 +16367,16 @@
         <v>10.59</v>
       </c>
       <c r="F23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I23" t="s">
         <v>77</v>
       </c>
       <c r="J23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K23" t="s">
         <v>27</v>
@@ -16473,13 +16471,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I25" t="s">
         <v>46</v>
       </c>
       <c r="J25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K25" t="s">
         <v>92</v>
@@ -16523,13 +16521,13 @@
         <v>11.03</v>
       </c>
       <c r="G26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I26" t="s">
         <v>46</v>
       </c>
       <c r="J26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K26" t="s">
         <v>92</v>
@@ -16933,13 +16931,13 @@
         <v>11.08</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I34" t="s">
         <v>81</v>
       </c>
       <c r="J34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K34" t="s">
         <v>43</v>
@@ -16948,7 +16946,7 @@
         <v>28</v>
       </c>
       <c r="N34" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O34">
         <f t="shared" ref="O34:O67" si="7">(INT(D34)*60+(D34-INT(D34))*100)-(INT($D$2)*60+($D$2-INT($D$2))*100)</f>
@@ -16984,13 +16982,13 @@
         <v>11.09</v>
       </c>
       <c r="G35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I35" t="s">
         <v>46</v>
       </c>
       <c r="J35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K35" t="s">
         <v>92</v>
@@ -17288,13 +17286,13 @@
         <v>11.13</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I41" s="19" t="s">
         <v>81</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K41" s="19" t="s">
         <v>27</v>
@@ -17304,7 +17302,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O41">
         <f t="shared" si="7"/>
@@ -17392,13 +17390,13 @@
         <v>11.15</v>
       </c>
       <c r="G43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I43" t="s">
         <v>46</v>
       </c>
       <c r="J43" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K43" t="s">
         <v>92</v>
@@ -17443,7 +17441,7 @@
         <v>11.15</v>
       </c>
       <c r="F44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>32</v>
@@ -17461,7 +17459,7 @@
         <v>35</v>
       </c>
       <c r="N44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O44">
         <f t="shared" si="7"/>
@@ -17497,7 +17495,7 @@
         <v>11.16</v>
       </c>
       <c r="F45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>32</v>
@@ -17515,7 +17513,7 @@
         <v>35</v>
       </c>
       <c r="N45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O45">
         <f t="shared" si="7"/>
@@ -17551,7 +17549,7 @@
         <v>11.17</v>
       </c>
       <c r="F46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>32</v>
@@ -17569,7 +17567,7 @@
         <v>35</v>
       </c>
       <c r="N46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O46">
         <f t="shared" si="7"/>
@@ -17966,7 +17964,7 @@
         <v>11.23</v>
       </c>
       <c r="F54" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G54" t="s">
         <v>110</v>
@@ -18021,16 +18019,16 @@
         <v>11.23</v>
       </c>
       <c r="F55" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I55" t="s">
         <v>46</v>
       </c>
       <c r="J55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K55" t="s">
         <v>92</v>
@@ -18075,7 +18073,7 @@
         <v>11.24</v>
       </c>
       <c r="F56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>32</v>
@@ -18093,7 +18091,7 @@
         <v>35</v>
       </c>
       <c r="N56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O56">
         <f t="shared" si="7"/>
@@ -18128,7 +18126,7 @@
         <v>11.25</v>
       </c>
       <c r="F57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G57" s="11" t="s">
         <v>32</v>
@@ -18146,7 +18144,7 @@
         <v>35</v>
       </c>
       <c r="N57" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O57">
         <f t="shared" si="7"/>
@@ -18181,7 +18179,7 @@
         <v>11.26</v>
       </c>
       <c r="F58" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>32</v>
@@ -18199,7 +18197,7 @@
         <v>35</v>
       </c>
       <c r="N58" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O58">
         <f t="shared" si="7"/>
@@ -18235,7 +18233,7 @@
         <v>11.27</v>
       </c>
       <c r="F59" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>32</v>
@@ -18289,7 +18287,7 @@
         <v>11.28</v>
       </c>
       <c r="F60" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G60" s="11" t="s">
         <v>32</v>
@@ -18344,7 +18342,7 @@
         <v>11.29</v>
       </c>
       <c r="F61" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G61" t="s">
         <v>69</v>
@@ -18385,7 +18383,7 @@
         <v>11.31</v>
       </c>
       <c r="F62" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G62" t="s">
         <v>85</v>
@@ -18439,7 +18437,7 @@
         <v>11.32</v>
       </c>
       <c r="F63" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G63" t="s">
         <v>51</v>
@@ -18493,7 +18491,7 @@
         <v>11.33</v>
       </c>
       <c r="F64" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>32</v>
@@ -18511,7 +18509,7 @@
         <v>35</v>
       </c>
       <c r="N64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O64">
         <f t="shared" si="7"/>
@@ -18546,7 +18544,7 @@
         <v>11.35</v>
       </c>
       <c r="F65" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>32</v>
@@ -18564,7 +18562,7 @@
         <v>35</v>
       </c>
       <c r="N65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O65">
         <f t="shared" si="7"/>
@@ -18600,7 +18598,7 @@
         <v>11.35</v>
       </c>
       <c r="F66" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>32</v>
@@ -18618,7 +18616,7 @@
         <v>35</v>
       </c>
       <c r="N66" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O66">
         <f t="shared" si="7"/>
@@ -18629,11 +18627,11 @@
         <v>59</v>
       </c>
       <c r="Q66">
-        <f t="shared" ref="Q66:Q97" si="14">P66-O66</f>
+        <f t="shared" ref="Q66:Q67" si="14">P66-O66</f>
         <v>0</v>
       </c>
       <c r="R66" t="str">
-        <f t="shared" ref="R66:R97" si="15">IF(Q66=0,"&lt;1 second","&lt;"&amp;(ROUND(Q66,2)+1)&amp;" seconds")</f>
+        <f t="shared" ref="R66:R67" si="15">IF(Q66=0,"&lt;1 second","&lt;"&amp;(ROUND(Q66,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S66">
@@ -18654,7 +18652,7 @@
         <v>11.36</v>
       </c>
       <c r="F67" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G67" s="11" t="s">
         <v>32</v>
@@ -18838,13 +18836,13 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" t="s">
         <v>214</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>215</v>
-      </c>
-      <c r="C2" t="s">
-        <v>216</v>
       </c>
       <c r="D2" s="3">
         <v>61.28</v>
@@ -18853,7 +18851,7 @@
         <v>61.29</v>
       </c>
       <c r="F2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G2" t="s">
         <v>71</v>
@@ -18904,10 +18902,10 @@
         <v>61.3</v>
       </c>
       <c r="F3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>218</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>219</v>
       </c>
       <c r="I3" t="s">
         <v>33</v>
@@ -19057,10 +19055,10 @@
         <v>61.33</v>
       </c>
       <c r="F6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I6" t="s">
         <v>29</v>
@@ -19108,10 +19106,10 @@
         <v>61.33</v>
       </c>
       <c r="F7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I7" t="s">
         <v>29</v>
@@ -19159,7 +19157,7 @@
         <v>61.33</v>
       </c>
       <c r="F8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G8" t="s">
         <v>51</v>
@@ -19210,7 +19208,7 @@
         <v>61.34</v>
       </c>
       <c r="F9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G9" t="s">
         <v>109</v>
@@ -19261,10 +19259,10 @@
         <v>61.36</v>
       </c>
       <c r="F10" t="s">
+        <v>217</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>218</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>219</v>
       </c>
       <c r="I10" t="s">
         <v>33</v>
@@ -19312,7 +19310,7 @@
         <v>61.38</v>
       </c>
       <c r="F11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>32</v>
@@ -19363,10 +19361,10 @@
         <v>61.39</v>
       </c>
       <c r="F12" t="s">
+        <v>223</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>224</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>225</v>
       </c>
       <c r="I12" t="s">
         <v>25</v>
@@ -19414,16 +19412,16 @@
         <v>61.41</v>
       </c>
       <c r="F13" t="s">
+        <v>225</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="I13" t="s">
         <v>227</v>
       </c>
-      <c r="I13" t="s">
-        <v>228</v>
-      </c>
       <c r="J13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K13" t="s">
         <v>43</v>
@@ -19465,10 +19463,10 @@
         <v>61.42</v>
       </c>
       <c r="F14" t="s">
+        <v>223</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>224</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>225</v>
       </c>
       <c r="I14" t="s">
         <v>25</v>
@@ -19515,7 +19513,7 @@
         <v>61.44</v>
       </c>
       <c r="F15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G15" t="s">
         <v>85</v>
@@ -19566,16 +19564,16 @@
         <v>61.45</v>
       </c>
       <c r="F16" t="s">
+        <v>225</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="I16" t="s">
         <v>227</v>
       </c>
-      <c r="I16" t="s">
-        <v>228</v>
-      </c>
       <c r="J16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K16" t="s">
         <v>43</v>
@@ -19616,7 +19614,7 @@
         <v>61.46</v>
       </c>
       <c r="F17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G17" t="s">
         <v>50</v>
@@ -19667,10 +19665,10 @@
         <v>61.46</v>
       </c>
       <c r="F18" t="s">
+        <v>230</v>
+      </c>
+      <c r="G18" s="14" t="s">
         <v>231</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>232</v>
       </c>
       <c r="I18" t="s">
         <v>46</v>
@@ -19718,10 +19716,10 @@
         <v>61.47</v>
       </c>
       <c r="F19" t="s">
+        <v>232</v>
+      </c>
+      <c r="G19" s="14" t="s">
         <v>233</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>234</v>
       </c>
       <c r="I19" t="s">
         <v>46</v>
@@ -19769,16 +19767,16 @@
         <v>61.48</v>
       </c>
       <c r="F20" t="s">
+        <v>234</v>
+      </c>
+      <c r="G20" s="14" t="s">
         <v>235</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>236</v>
       </c>
       <c r="I20" t="s">
         <v>57</v>
       </c>
       <c r="J20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K20" t="s">
         <v>27</v>
@@ -19820,10 +19818,10 @@
         <v>61.49</v>
       </c>
       <c r="F21" t="s">
+        <v>237</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>238</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>239</v>
       </c>
       <c r="I21" t="s">
         <v>74</v>
@@ -19871,7 +19869,7 @@
         <v>61.49</v>
       </c>
       <c r="F22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G22" t="s">
         <v>51</v>
@@ -19922,7 +19920,7 @@
         <v>61.5</v>
       </c>
       <c r="F23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G23" t="s">
         <v>24</v>
@@ -19973,7 +19971,7 @@
         <v>61.5</v>
       </c>
       <c r="F24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G24" t="s">
         <v>51</v>
@@ -20023,16 +20021,16 @@
         <v>61.55</v>
       </c>
       <c r="F25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I25" t="s">
         <v>77</v>
       </c>
       <c r="J25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K25" t="s">
         <v>27</v>
@@ -20073,16 +20071,16 @@
         <v>61.57</v>
       </c>
       <c r="F26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I26" t="s">
         <v>83</v>
       </c>
       <c r="J26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K26" t="s">
         <v>27</v>
@@ -20123,16 +20121,16 @@
         <v>61.59</v>
       </c>
       <c r="F27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I27" t="s">
         <v>83</v>
       </c>
       <c r="J27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K27" t="s">
         <v>27</v>
@@ -20224,16 +20222,16 @@
         <v>62.06</v>
       </c>
       <c r="F29" t="s">
+        <v>244</v>
+      </c>
+      <c r="G29" s="14" t="s">
         <v>245</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>246</v>
       </c>
       <c r="I29" t="s">
         <v>96</v>
       </c>
       <c r="J29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K29" t="s">
         <v>27</v>
@@ -20275,7 +20273,7 @@
         <v>62.06</v>
       </c>
       <c r="F30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>32</v>
@@ -20326,7 +20324,7 @@
         <v>62.07</v>
       </c>
       <c r="F31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G31" t="s">
         <v>24</v>
@@ -20377,7 +20375,7 @@
         <v>62.08</v>
       </c>
       <c r="F32" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G32" t="s">
         <v>51</v>
@@ -20427,7 +20425,7 @@
         <v>62.24</v>
       </c>
       <c r="F33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G33" t="s">
         <v>99</v>
@@ -20517,7 +20515,7 @@
         <v>62.24</v>
       </c>
       <c r="F35" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G35" t="s">
         <v>51</v>
@@ -20568,16 +20566,16 @@
         <v>62.25</v>
       </c>
       <c r="F36" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I36" t="s">
         <v>77</v>
       </c>
       <c r="J36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K36" t="s">
         <v>27</v>
@@ -20618,16 +20616,16 @@
         <v>62.28</v>
       </c>
       <c r="F37" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G37" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I37" t="s">
         <v>77</v>
       </c>
       <c r="J37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K37" t="s">
         <v>27</v>
@@ -20927,13 +20925,13 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" t="s">
         <v>254</v>
-      </c>
-      <c r="C2" t="s">
-        <v>255</v>
       </c>
       <c r="D2" s="3">
         <v>24.33</v>
@@ -20943,7 +20941,7 @@
         <v>24.33</v>
       </c>
       <c r="F2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G2" t="s">
         <v>56</v>
@@ -20994,7 +20992,7 @@
         <v>24.32</v>
       </c>
       <c r="F3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G3" t="s">
         <v>51</v>
@@ -21044,10 +21042,10 @@
         <v>24.3</v>
       </c>
       <c r="F4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>257</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>258</v>
       </c>
       <c r="I4" s="19" t="s">
         <v>115</v>
@@ -21095,7 +21093,7 @@
         <v>24.29</v>
       </c>
       <c r="F5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G5" t="s">
         <v>45</v>
@@ -21145,7 +21143,7 @@
         <v>24.27</v>
       </c>
       <c r="F6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G6" t="s">
         <v>56</v>
@@ -21196,7 +21194,7 @@
         <v>24.27</v>
       </c>
       <c r="F7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G7" t="s">
         <v>45</v>
@@ -21247,7 +21245,7 @@
         <v>24.26</v>
       </c>
       <c r="F8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>32</v>
@@ -21298,7 +21296,7 @@
         <v>24.26</v>
       </c>
       <c r="F9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>32</v>
@@ -21348,10 +21346,10 @@
         <v>24.23</v>
       </c>
       <c r="F10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>262</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>263</v>
       </c>
       <c r="I10" t="s">
         <v>33</v>
@@ -21399,10 +21397,10 @@
         <v>24.22</v>
       </c>
       <c r="F11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I11" t="s">
         <v>46</v>
@@ -21450,16 +21448,16 @@
         <v>24.21</v>
       </c>
       <c r="F12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I12" t="s">
         <v>81</v>
       </c>
       <c r="J12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K12" t="s">
         <v>43</v>
@@ -21501,7 +21499,7 @@
         <v>24.2</v>
       </c>
       <c r="F13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G13" t="s">
         <v>109</v>
@@ -21552,7 +21550,7 @@
         <v>24.17</v>
       </c>
       <c r="F14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G14" t="s">
         <v>85</v>
@@ -21654,7 +21652,7 @@
         <v>24.16</v>
       </c>
       <c r="F16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G16" t="s">
         <v>51</v>
@@ -21705,10 +21703,10 @@
         <v>24.15</v>
       </c>
       <c r="F17" t="s">
+        <v>265</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>266</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>267</v>
       </c>
       <c r="I17" s="19" t="s">
         <v>77</v>
@@ -21755,10 +21753,10 @@
         <v>24.14</v>
       </c>
       <c r="F18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I18" t="s">
         <v>46</v>
@@ -21805,10 +21803,10 @@
         <v>24.13</v>
       </c>
       <c r="F19" t="s">
+        <v>268</v>
+      </c>
+      <c r="G19" s="14" t="s">
         <v>269</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>270</v>
       </c>
       <c r="I19" t="s">
         <v>77</v>
@@ -21856,10 +21854,10 @@
         <v>24.12</v>
       </c>
       <c r="F20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I20" s="19" t="s">
         <v>77</v>
@@ -21907,10 +21905,10 @@
         <v>24.12</v>
       </c>
       <c r="F21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I21" t="s">
         <v>77</v>
@@ -21958,7 +21956,7 @@
         <v>24.11</v>
       </c>
       <c r="F22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G22" t="s">
         <v>45</v>
@@ -22009,16 +22007,16 @@
         <v>24.1</v>
       </c>
       <c r="F23" t="s">
+        <v>273</v>
+      </c>
+      <c r="G23" s="14" t="s">
         <v>274</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>275</v>
       </c>
       <c r="I23" s="19" t="s">
         <v>83</v>
       </c>
       <c r="J23" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K23" t="s">
         <v>27</v>
@@ -22111,7 +22109,7 @@
         <v>24.09</v>
       </c>
       <c r="F25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G25" t="s">
         <v>51</v>
@@ -22161,10 +22159,10 @@
         <v>24.08</v>
       </c>
       <c r="F26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I26" s="19" t="s">
         <v>77</v>
@@ -22212,10 +22210,10 @@
         <v>24.07</v>
       </c>
       <c r="F27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I27" t="s">
         <v>77</v>
@@ -22262,7 +22260,7 @@
         <v>24.05</v>
       </c>
       <c r="F28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>32</v>
@@ -22414,16 +22412,16 @@
         <v>23.56</v>
       </c>
       <c r="F31" t="s">
+        <v>279</v>
+      </c>
+      <c r="G31" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="I31" t="s">
         <v>281</v>
       </c>
-      <c r="I31" t="s">
-        <v>282</v>
-      </c>
       <c r="J31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K31" t="s">
         <v>27</v>
@@ -22516,7 +22514,7 @@
         <v>23.55</v>
       </c>
       <c r="F33" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O33">
         <f t="shared" si="0"/>
@@ -22551,16 +22549,16 @@
         <v>23.54</v>
       </c>
       <c r="F34" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I34" t="s">
         <v>77</v>
       </c>
       <c r="J34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K34" t="s">
         <v>27</v>
@@ -22602,16 +22600,16 @@
         <v>23.53</v>
       </c>
       <c r="F35" t="s">
+        <v>279</v>
+      </c>
+      <c r="G35" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="G35" s="14" t="s">
+      <c r="I35" t="s">
         <v>281</v>
       </c>
-      <c r="I35" t="s">
-        <v>282</v>
-      </c>
       <c r="J35" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K35" t="s">
         <v>43</v>
@@ -22652,7 +22650,7 @@
         <v>23.5</v>
       </c>
       <c r="F36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G36" t="s">
         <v>121</v>
@@ -22702,10 +22700,10 @@
         <v>23.47</v>
       </c>
       <c r="F37" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I37" t="s">
         <v>46</v>
@@ -22753,7 +22751,7 @@
         <v>23.45</v>
       </c>
       <c r="F38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>32</v>
@@ -22855,7 +22853,7 @@
         <v>23.44</v>
       </c>
       <c r="F40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G40" t="s">
         <v>51</v>
@@ -22906,16 +22904,16 @@
         <v>23.44</v>
       </c>
       <c r="F41" t="s">
+        <v>286</v>
+      </c>
+      <c r="G41" s="14" t="s">
         <v>287</v>
-      </c>
-      <c r="G41" s="14" t="s">
-        <v>288</v>
       </c>
       <c r="I41" s="19" t="s">
         <v>77</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K41" t="s">
         <v>27</v>
@@ -22956,7 +22954,7 @@
         <v>23.4</v>
       </c>
       <c r="F42" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G42" t="s">
         <v>121</v>
@@ -23007,7 +23005,7 @@
         <v>23.32</v>
       </c>
       <c r="F43" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G43" s="11" t="s">
         <v>32</v>
@@ -23058,7 +23056,7 @@
         <v>23.28</v>
       </c>
       <c r="F44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G44" t="s">
         <v>121</v>
@@ -23101,226 +23099,115 @@
       </c>
     </row>
     <row r="45" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="E45" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="E46" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="E47" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E47" s="3"/>
     </row>
     <row r="48" spans="4:20" x14ac:dyDescent="0.2">
-      <c r="E48" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E49" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E49" s="3"/>
     </row>
     <row r="50" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E50" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E51" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E52" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E53" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E54" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E54" s="3"/>
     </row>
     <row r="55" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E55" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E55" s="3"/>
     </row>
     <row r="56" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E56" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E56" s="3"/>
     </row>
     <row r="57" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E57" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E57" s="3"/>
     </row>
     <row r="58" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E58" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E59" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E60" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E61" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E61" s="3"/>
     </row>
     <row r="62" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E62" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E62" s="3"/>
     </row>
     <row r="63" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E63" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E63" s="3"/>
     </row>
     <row r="64" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E64" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E64" s="3"/>
     </row>
     <row r="65" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E65" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E65" s="3"/>
     </row>
     <row r="66" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E66" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E66" s="3"/>
     </row>
     <row r="67" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E67" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E67" s="3"/>
     </row>
     <row r="68" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E68" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E68" s="3"/>
     </row>
     <row r="69" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E69" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E69" s="3"/>
     </row>
     <row r="70" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E70" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E70" s="3"/>
     </row>
     <row r="71" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E71" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E71" s="3"/>
     </row>
     <row r="72" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E72" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E72" s="3"/>
     </row>
     <row r="73" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E73" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E73" s="3"/>
     </row>
     <row r="74" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E74" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E74" s="3"/>
     </row>
     <row r="75" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E75" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E75" s="3"/>
     </row>
     <row r="76" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E76" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E76" s="3"/>
     </row>
     <row r="77" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E77" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E77" s="3"/>
     </row>
     <row r="78" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E78" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E78" s="3"/>
     </row>
     <row r="79" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E79" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E79" s="3"/>
     </row>
     <row r="80" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E80" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E80" s="3"/>
     </row>
     <row r="81" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E81" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="E81" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23461,13 +23348,13 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" t="s">
         <v>292</v>
-      </c>
-      <c r="C2" t="s">
-        <v>293</v>
       </c>
       <c r="D2" s="3">
         <v>94.02</v>
@@ -23477,7 +23364,7 @@
         <v>94.02</v>
       </c>
       <c r="F2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G2" t="s">
         <v>51</v>
@@ -23528,7 +23415,7 @@
         <v>94.02</v>
       </c>
       <c r="F3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G3" t="s">
         <v>24</v>
@@ -23579,7 +23466,7 @@
         <v>94.03</v>
       </c>
       <c r="F4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G4" t="s">
         <v>45</v>
@@ -23629,7 +23516,7 @@
         <v>94.05</v>
       </c>
       <c r="F5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G5" t="s">
         <v>90</v>
@@ -23679,16 +23566,16 @@
         <v>94.1</v>
       </c>
       <c r="F6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I6" t="s">
         <v>46</v>
       </c>
       <c r="J6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K6" t="s">
         <v>92</v>
@@ -23730,7 +23617,7 @@
         <v>94.11</v>
       </c>
       <c r="F7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G7" t="s">
         <v>117</v>
@@ -23781,16 +23668,16 @@
         <v>94.13</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
+        <v>226</v>
+      </c>
+      <c r="I8" t="s">
         <v>227</v>
       </c>
-      <c r="I8" t="s">
-        <v>228</v>
-      </c>
       <c r="J8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K8" t="s">
         <v>43</v>
@@ -23832,7 +23719,7 @@
         <v>94.15</v>
       </c>
       <c r="F9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G9" t="s">
         <v>32</v>
@@ -23883,7 +23770,7 @@
         <v>94.16</v>
       </c>
       <c r="F10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G10" t="s">
         <v>32</v>
@@ -23934,16 +23821,16 @@
         <v>94.17</v>
       </c>
       <c r="F11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I11" t="s">
         <v>57</v>
       </c>
       <c r="J11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
         <v>27</v>
@@ -23984,7 +23871,7 @@
         <v>94.21</v>
       </c>
       <c r="F12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G12" t="s">
         <v>82</v>
@@ -24034,7 +23921,7 @@
         <v>94.23</v>
       </c>
       <c r="F13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
@@ -24085,7 +23972,7 @@
         <v>94.25</v>
       </c>
       <c r="F14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -24135,7 +24022,7 @@
         <v>94.28</v>
       </c>
       <c r="F15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G15" t="s">
         <v>85</v>
@@ -24185,10 +24072,10 @@
         <v>94.29</v>
       </c>
       <c r="F16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I16" s="19" t="s">
         <v>77</v>
@@ -24236,10 +24123,10 @@
         <v>94.3</v>
       </c>
       <c r="F17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I17" s="19" t="s">
         <v>77</v>
@@ -24288,7 +24175,7 @@
         <v>94.3</v>
       </c>
       <c r="G18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I18" s="19" t="s">
         <v>77</v>
@@ -24337,7 +24224,7 @@
         <v>94.3</v>
       </c>
       <c r="G19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I19" s="19" t="s">
         <v>77</v>
@@ -24385,7 +24272,7 @@
         <v>94.32</v>
       </c>
       <c r="G20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I20" s="19" t="s">
         <v>77</v>
@@ -24433,7 +24320,7 @@
         <v>94.33</v>
       </c>
       <c r="G21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I21" s="19" t="s">
         <v>77</v>
@@ -24481,7 +24368,7 @@
         <v>94.34</v>
       </c>
       <c r="G22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I22" s="19" t="s">
         <v>77</v>
@@ -24529,7 +24416,7 @@
         <v>94.35</v>
       </c>
       <c r="G23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I23" s="19" t="s">
         <v>77</v>
@@ -24577,7 +24464,7 @@
         <v>94.37</v>
       </c>
       <c r="G24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I24" s="19" t="s">
         <v>77</v>
@@ -24720,7 +24607,7 @@
         <v>94.45</v>
       </c>
       <c r="F27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G27" t="s">
         <v>51</v>
@@ -24771,10 +24658,10 @@
         <v>94.45</v>
       </c>
       <c r="F28" t="s">
+        <v>308</v>
+      </c>
+      <c r="G28" s="15" t="s">
         <v>309</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>310</v>
       </c>
       <c r="I28" s="19" t="s">
         <v>25</v>
@@ -24823,7 +24710,7 @@
         <v>94.48</v>
       </c>
       <c r="G29" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I29" t="s">
         <v>81</v>
@@ -24870,7 +24757,7 @@
         <v>94.5</v>
       </c>
       <c r="F30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G30" t="s">
         <v>32</v>
@@ -24920,10 +24807,10 @@
         <v>94.52</v>
       </c>
       <c r="F31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I31" t="s">
         <v>115</v>
@@ -24971,7 +24858,7 @@
         <v>94.53</v>
       </c>
       <c r="F32" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G32" t="s">
         <v>32</v>
@@ -25021,16 +24908,16 @@
         <v>94.57</v>
       </c>
       <c r="F33" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G33" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I33" t="s">
         <v>46</v>
       </c>
       <c r="J33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K33" t="s">
         <v>92</v>
@@ -25120,7 +25007,7 @@
         <v>94.58</v>
       </c>
       <c r="G35" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I35" t="s">
         <v>29</v>
@@ -25524,10 +25411,10 @@
         <v>21</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2" t="s">
         <v>316</v>
-      </c>
-      <c r="C2" t="s">
-        <v>317</v>
       </c>
       <c r="D2" s="3">
         <v>14.57</v>
@@ -25536,7 +25423,7 @@
         <v>14.59</v>
       </c>
       <c r="F2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G2" t="s">
         <v>121</v>
@@ -25586,16 +25473,16 @@
         <v>14.59</v>
       </c>
       <c r="F3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I3" t="s">
         <v>46</v>
       </c>
       <c r="J3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K3" t="s">
         <v>92</v>
@@ -25636,7 +25523,7 @@
         <v>15.01</v>
       </c>
       <c r="F4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G4" t="s">
         <v>32</v>
@@ -25784,7 +25671,7 @@
         <v>15.14</v>
       </c>
       <c r="F7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G7" t="s">
         <v>32</v>
@@ -25835,17 +25722,17 @@
         <v>15.14</v>
       </c>
       <c r="F8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G8" s="19" t="s">
         <v>322</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>323</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19" t="s">
         <v>57</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K8" s="19" t="s">
         <v>27</v>
@@ -25887,7 +25774,7 @@
         <v>15.16</v>
       </c>
       <c r="F9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G9" t="s">
         <v>76</v>
@@ -25937,7 +25824,7 @@
         <v>15.27</v>
       </c>
       <c r="F10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G10" t="s">
         <v>32</v>
@@ -25988,17 +25875,17 @@
         <v>15.27</v>
       </c>
       <c r="F11" t="s">
+        <v>321</v>
+      </c>
+      <c r="G11" s="19" t="s">
         <v>322</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>323</v>
       </c>
       <c r="H11" s="19"/>
       <c r="I11" s="19" t="s">
         <v>57</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K11" s="19" t="s">
         <v>27</v>
@@ -26040,7 +25927,7 @@
         <v>15.29</v>
       </c>
       <c r="G12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I12" t="s">
         <v>77</v>
@@ -26135,14 +26022,14 @@
         <v>15.35</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="19" t="s">
         <v>57</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K14" s="19" t="s">
         <v>27</v>
@@ -26328,7 +26215,7 @@
         <v>15.4</v>
       </c>
       <c r="F18" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G18" t="s">
         <v>32</v>
@@ -26378,7 +26265,7 @@
         <v>15.44</v>
       </c>
       <c r="F19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G19" t="s">
         <v>32</v>
@@ -26429,7 +26316,7 @@
         <v>15.44</v>
       </c>
       <c r="G20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I20" t="s">
         <v>115</v>
@@ -26477,7 +26364,7 @@
         <v>15.45</v>
       </c>
       <c r="F21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G21" t="s">
         <v>32</v>
@@ -26624,7 +26511,7 @@
         <v>15.46</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I24" t="s">
         <v>74</v>
@@ -26719,7 +26606,7 @@
         <v>15.47</v>
       </c>
       <c r="F26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G26" t="s">
         <v>32</v>
@@ -26769,13 +26656,13 @@
         <v>15.48</v>
       </c>
       <c r="G27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I27" t="s">
         <v>46</v>
       </c>
       <c r="J27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K27" t="s">
         <v>92</v>
@@ -26816,7 +26703,7 @@
         <v>15.49</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G28" t="s">
         <v>45</v>
@@ -26915,16 +26802,16 @@
         <v>15.49</v>
       </c>
       <c r="F30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I30" t="s">
         <v>46</v>
       </c>
       <c r="J30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K30" t="s">
         <v>92</v>
@@ -27062,7 +26949,7 @@
         <v>15.51</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I33" t="s">
         <v>74</v>
@@ -27158,13 +27045,13 @@
         <v>15.53</v>
       </c>
       <c r="G35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I35" t="s">
         <v>46</v>
       </c>
       <c r="J35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K35" t="s">
         <v>92</v>
@@ -27205,13 +27092,13 @@
         <v>15.54</v>
       </c>
       <c r="G36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I36" t="s">
         <v>46</v>
       </c>
       <c r="J36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K36" t="s">
         <v>92</v>
@@ -27299,13 +27186,13 @@
         <v>15.55</v>
       </c>
       <c r="G38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I38" t="s">
         <v>46</v>
       </c>
       <c r="J38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K38" t="s">
         <v>92</v>
@@ -27346,13 +27233,13 @@
         <v>15.56</v>
       </c>
       <c r="G39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I39" t="s">
         <v>46</v>
       </c>
       <c r="J39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K39" t="s">
         <v>92</v>
@@ -27753,7 +27640,7 @@
         <v>86.58</v>
       </c>
       <c r="G3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I3" t="s">
         <v>29</v>
@@ -27906,7 +27793,7 @@
         <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I6" t="s">
         <v>29</v>
@@ -28053,7 +27940,7 @@
         <v>87.04</v>
       </c>
       <c r="G9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I9" t="s">
         <v>29</v>
@@ -28397,7 +28284,7 @@
         <v>87.14</v>
       </c>
       <c r="G16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I16" t="s">
         <v>29</v>
@@ -28883,7 +28770,7 @@
         <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I26" t="s">
         <v>29</v>
@@ -28982,7 +28869,7 @@
         <v>40</v>
       </c>
       <c r="G28" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I28" t="s">
         <v>29</v>
@@ -29180,7 +29067,7 @@
         <v>87.26</v>
       </c>
       <c r="G32" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I32" t="s">
         <v>29</v>
@@ -29305,11 +29192,11 @@
         <v>35</v>
       </c>
       <c r="Q34">
-        <f t="shared" ref="Q34:Q65" si="11">P34-O34</f>
+        <f t="shared" ref="Q34:Q58" si="11">P34-O34</f>
         <v>0</v>
       </c>
       <c r="R34" t="str">
-        <f t="shared" ref="R34:R65" si="12">IF(Q34=0,"&lt;1 second","&lt;"&amp;(ROUND(Q34,2)+1)&amp;" seconds")</f>
+        <f t="shared" ref="R34:R58" si="12">IF(Q34=0,"&lt;1 second","&lt;"&amp;(ROUND(Q34,2)+1)&amp;" seconds")</f>
         <v>&lt;1 second</v>
       </c>
       <c r="S34">
@@ -29380,7 +29267,7 @@
         <v>40</v>
       </c>
       <c r="G36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I36" t="s">
         <v>29</v>
@@ -30148,7 +30035,7 @@
         <v>75</v>
       </c>
       <c r="G52" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I52" t="s">
         <v>29</v>
